--- a/Brew_Comparison.xlsx
+++ b/Brew_Comparison.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9266" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9266" uniqueCount="303">
   <si>
     <t>TIA Portal DB Instrument Status Comparison — Brew</t>
   </si>
@@ -111,469 +111,475 @@
     <t>AV208-1</t>
   </si>
   <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>EM - 208</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>DIFF</t>
+  </si>
+  <si>
+    <t>UPDATE: VLV_W_FB: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>AV210-1</t>
+  </si>
+  <si>
+    <t>EM - 210</t>
+  </si>
+  <si>
+    <t>UPDATE: EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>AV212-1</t>
+  </si>
+  <si>
+    <t>EM - 212</t>
+  </si>
+  <si>
+    <t>AV220-1</t>
+  </si>
+  <si>
+    <t>EM - 22X</t>
+  </si>
+  <si>
+    <t>AV221-1</t>
+  </si>
+  <si>
     <t>Unknown</t>
   </si>
   <si>
-    <t>EM - 208</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>DIFF</t>
+    <t>EM - 22Y</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>AV222-1</t>
+  </si>
+  <si>
+    <t>Unit Dch</t>
+  </si>
+  <si>
+    <t>EM - 222</t>
+  </si>
+  <si>
+    <t>AV301-1</t>
+  </si>
+  <si>
+    <t>EM - 300</t>
+  </si>
+  <si>
+    <t>AV320-1</t>
+  </si>
+  <si>
+    <t>AV340-1</t>
+  </si>
+  <si>
+    <t>EM - 340</t>
+  </si>
+  <si>
+    <t>AV340-2</t>
+  </si>
+  <si>
+    <t>AV460-1</t>
+  </si>
+  <si>
+    <t>AV460-2</t>
+  </si>
+  <si>
+    <t>AV460d-1</t>
+  </si>
+  <si>
+    <t>Unit Sep</t>
+  </si>
+  <si>
+    <t>EM - 460</t>
+  </si>
+  <si>
+    <t>AV543-1</t>
+  </si>
+  <si>
+    <t>EM - 506</t>
+  </si>
+  <si>
+    <t>AV463-1</t>
+  </si>
+  <si>
+    <t>EM - 463</t>
+  </si>
+  <si>
+    <t>AV463-2</t>
+  </si>
+  <si>
+    <t>AV461-1</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>NOT IN DB MAP</t>
+  </si>
+  <si>
+    <t>FIS409-1</t>
+  </si>
+  <si>
+    <t>COOLING LIQUID FLOW</t>
+  </si>
+  <si>
+    <t>EM - 400</t>
+  </si>
+  <si>
+    <t>FIS615-1</t>
+  </si>
+  <si>
+    <t>SEALING LIQUID FLOW INLET SEAL</t>
+  </si>
+  <si>
+    <t>EM - 600</t>
+  </si>
+  <si>
+    <t>FIS635-1</t>
+  </si>
+  <si>
+    <t>SEALING LIQUID FLOW OUTLET SEAL</t>
+  </si>
+  <si>
+    <t>FIS630-1</t>
+  </si>
+  <si>
+    <t>UPDATE: EXIST: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>PIS340-1</t>
+  </si>
+  <si>
+    <t>SAFETY LIQUID PRESSURE</t>
+  </si>
+  <si>
+    <t>PIS375-1</t>
+  </si>
+  <si>
+    <t>OP. LIQUID PRESSURE</t>
+  </si>
+  <si>
+    <t>EM - 375</t>
+  </si>
+  <si>
+    <t>PS502-1</t>
+  </si>
+  <si>
+    <t>INSTRUMENT AIR PRESSURE</t>
+  </si>
+  <si>
+    <t>EM - 100</t>
+  </si>
+  <si>
+    <t>QT201-1_OK</t>
+  </si>
+  <si>
+    <t>HEALTHY STATUS</t>
+  </si>
+  <si>
+    <t>QT220-1_OK</t>
   </si>
   <si>
     <t>UPDATE: ENABLE: DB=False-&gt;True</t>
   </si>
   <si>
-    <t>AV210-1</t>
-  </si>
-  <si>
-    <t>EM - 210</t>
+    <t>QT220-2_OK</t>
+  </si>
+  <si>
+    <t>NOT FOUND IN DB</t>
+  </si>
+  <si>
+    <t>eWON</t>
+  </si>
+  <si>
+    <t>eWON Talk2M STATUS</t>
+  </si>
+  <si>
+    <t>N/F</t>
+  </si>
+  <si>
+    <t>LA201-1</t>
+  </si>
+  <si>
+    <t>INLET SIGHT GLASS BACKLIGHT</t>
+  </si>
+  <si>
+    <t>LA220-1</t>
+  </si>
+  <si>
+    <t>OUTLET SIGHT GLASS BACKLIGHT</t>
+  </si>
+  <si>
+    <t>L-GN</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-GREEN LIGHT</t>
+  </si>
+  <si>
+    <t>L-YL</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-YELLOW LIGHT</t>
+  </si>
+  <si>
+    <t>L-RD</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-RED LIGHT/ALARM LIGHT</t>
+  </si>
+  <si>
+    <t>L-BUZZ</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-BUZZIER</t>
+  </si>
+  <si>
+    <t>LA221-1</t>
+  </si>
+  <si>
+    <t>PIT201-1</t>
+  </si>
+  <si>
+    <t>INLET PRESSURE</t>
+  </si>
+  <si>
+    <t>PIT22X-1</t>
+  </si>
+  <si>
+    <t>SEPARATOR OUTLET 220 PRESSURE</t>
+  </si>
+  <si>
+    <t>QT201-1</t>
+  </si>
+  <si>
+    <t>INLET TURBIDITY</t>
+  </si>
+  <si>
+    <t>QT220-1</t>
+  </si>
+  <si>
+    <t>OUTLET TURBIDITY</t>
+  </si>
+  <si>
+    <t>QT220-2</t>
+  </si>
+  <si>
+    <t>PIT22Y-1</t>
+  </si>
+  <si>
+    <t>SEPARATOR OUTLET 221 PRESSURE</t>
+  </si>
+  <si>
+    <t>PIT222-1</t>
+  </si>
+  <si>
+    <t>SOLIDS OUTLET PRESSURE</t>
+  </si>
+  <si>
+    <t>LT-BT</t>
+  </si>
+  <si>
+    <t>BUFFER TANK LEVEL</t>
+  </si>
+  <si>
+    <t>LT463-1</t>
+  </si>
+  <si>
+    <t>LEVEL IN B463-1</t>
+  </si>
+  <si>
+    <t>PIT463-1</t>
+  </si>
+  <si>
+    <t>E-MOTION PRESSURE</t>
+  </si>
+  <si>
+    <t>TT406-1</t>
+  </si>
+  <si>
+    <t>COOLING LIQUID TEMPERATURE</t>
+  </si>
+  <si>
+    <t>EM - 430</t>
+  </si>
+  <si>
+    <t>FIT201-1</t>
+  </si>
+  <si>
+    <t>FEED FLOW</t>
+  </si>
+  <si>
+    <t>FIT208-1</t>
+  </si>
+  <si>
+    <t>BLENDING FLOW</t>
+  </si>
+  <si>
+    <t>FIT409-1</t>
+  </si>
+  <si>
+    <t>FCV201-1</t>
+  </si>
+  <si>
+    <t>PCV22X-1</t>
+  </si>
+  <si>
+    <t>BACK PRESSURE 220</t>
+  </si>
+  <si>
+    <t>IP506A</t>
+  </si>
+  <si>
+    <t>DISCHARGE PRESSURE</t>
+  </si>
+  <si>
+    <t>PCV22Y-1</t>
+  </si>
+  <si>
+    <t>BACK PRESSURE 221</t>
+  </si>
+  <si>
+    <t>FCV208-1</t>
+  </si>
+  <si>
+    <t>FCV210-1</t>
+  </si>
+  <si>
+    <t>RECIRCULATION FLOW</t>
+  </si>
+  <si>
+    <t>FCV430-1</t>
+  </si>
+  <si>
+    <t>GLYCOL FLOW</t>
+  </si>
+  <si>
+    <t>FCV409-1</t>
+  </si>
+  <si>
+    <t>COOLING LIQUID FLOW CONTROL VALVE</t>
+  </si>
+  <si>
+    <t>ST74X</t>
+  </si>
+  <si>
+    <t>SPEED SENSOR PULSES</t>
+  </si>
+  <si>
+    <t>ST749</t>
+  </si>
+  <si>
+    <t>SPEED SENSOR ALFDEX</t>
+  </si>
+  <si>
+    <t>EMS</t>
+  </si>
+  <si>
+    <t>E-STOP</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>UPS BATTERY</t>
+  </si>
+  <si>
+    <t>P+F OS</t>
+  </si>
+  <si>
+    <t>OVERSPEED</t>
+  </si>
+  <si>
+    <t>EM - 740</t>
+  </si>
+  <si>
+    <t>P+F ERROR</t>
+  </si>
+  <si>
+    <t>ERROR</t>
+  </si>
+  <si>
+    <t>TS222-1</t>
+  </si>
+  <si>
+    <t>SOLIDS PUMP TEMPERATURE</t>
+  </si>
+  <si>
+    <t>UPDATE: EXIST: DB=False-&gt;True</t>
+  </si>
+  <si>
+    <t>TS730</t>
+  </si>
+  <si>
+    <t>MOTOR WINDINGS TEMPERATURE</t>
+  </si>
+  <si>
+    <t>EM - 730</t>
+  </si>
+  <si>
+    <t>UPDATE: ENABLE: DB=True-&gt;False, EXIST: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>LS222-1</t>
+  </si>
+  <si>
+    <t>HIGH-HIGH LEVEL IN CYCLONE</t>
+  </si>
+  <si>
+    <t>LS222-2</t>
+  </si>
+  <si>
+    <t>HIGH LEVEL IN CYCLONE</t>
+  </si>
+  <si>
+    <t>LS222-3</t>
+  </si>
+  <si>
+    <t>LOW LEVEL IN CYCLONE</t>
+  </si>
+  <si>
+    <t>M701</t>
+  </si>
+  <si>
+    <t>SEPARATOR VFD TRIP FB</t>
+  </si>
+  <si>
+    <t>EM - 701</t>
+  </si>
+  <si>
+    <t>P222-1</t>
+  </si>
+  <si>
+    <t>SOLIDS PUMP RUN FB</t>
+  </si>
+  <si>
+    <t>P403-1</t>
+  </si>
+  <si>
+    <t>OIL COOLING PUMP RUN FB</t>
+  </si>
+  <si>
+    <t>EM - 420</t>
+  </si>
+  <si>
+    <t>P406-1</t>
+  </si>
+  <si>
+    <t>COOLING RECIRC PUMP RUN FB</t>
   </si>
   <si>
     <t>UPDATE: ENABLE: DB=False-&gt;True, EXIST: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>AV212-1</t>
-  </si>
-  <si>
-    <t>EM - 212</t>
-  </si>
-  <si>
-    <t>AV220-1</t>
-  </si>
-  <si>
-    <t>EM - 22X</t>
-  </si>
-  <si>
-    <t>AV221-1</t>
-  </si>
-  <si>
-    <t>EM - 22Y</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>UPDATE: EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>AV222-1</t>
-  </si>
-  <si>
-    <t>Unit Dch</t>
-  </si>
-  <si>
-    <t>EM - 222</t>
-  </si>
-  <si>
-    <t>AV301-1</t>
-  </si>
-  <si>
-    <t>EM - 300</t>
-  </si>
-  <si>
-    <t>AV320-1</t>
-  </si>
-  <si>
-    <t>AV340-1</t>
-  </si>
-  <si>
-    <t>EM - 340</t>
-  </si>
-  <si>
-    <t>AV340-2</t>
-  </si>
-  <si>
-    <t>AV460-1</t>
-  </si>
-  <si>
-    <t>AV460-2</t>
-  </si>
-  <si>
-    <t>AV460d-1</t>
-  </si>
-  <si>
-    <t>Unit Sep</t>
-  </si>
-  <si>
-    <t>EM - 460</t>
-  </si>
-  <si>
-    <t>AV543-1</t>
-  </si>
-  <si>
-    <t>EM - 506</t>
-  </si>
-  <si>
-    <t>AV463-1</t>
-  </si>
-  <si>
-    <t>EM - 463</t>
-  </si>
-  <si>
-    <t>AV463-2</t>
-  </si>
-  <si>
-    <t>AV461-1</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>NOT IN DB MAP</t>
-  </si>
-  <si>
-    <t>FIS409-1</t>
-  </si>
-  <si>
-    <t>COOLING LIQUID FLOW</t>
-  </si>
-  <si>
-    <t>EM - 400</t>
-  </si>
-  <si>
-    <t>FIS615-1</t>
-  </si>
-  <si>
-    <t>SEALING LIQUID FLOW INLET SEAL</t>
-  </si>
-  <si>
-    <t>EM - 600</t>
-  </si>
-  <si>
-    <t>FIS635-1</t>
-  </si>
-  <si>
-    <t>SEALING LIQUID FLOW OUTLET SEAL</t>
-  </si>
-  <si>
-    <t>FIS630-1</t>
-  </si>
-  <si>
-    <t>UPDATE: EXIST: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>PIS340-1</t>
-  </si>
-  <si>
-    <t>SAFETY LIQUID PRESSURE</t>
-  </si>
-  <si>
-    <t>PIS375-1</t>
-  </si>
-  <si>
-    <t>OP. LIQUID PRESSURE</t>
-  </si>
-  <si>
-    <t>EM - 375</t>
-  </si>
-  <si>
-    <t>PS502-1</t>
-  </si>
-  <si>
-    <t>INSTRUMENT AIR PRESSURE</t>
-  </si>
-  <si>
-    <t>EM - 100</t>
-  </si>
-  <si>
-    <t>QT201-1_OK</t>
-  </si>
-  <si>
-    <t>HEALTHY STATUS</t>
-  </si>
-  <si>
-    <t>QT220-1_OK</t>
-  </si>
-  <si>
-    <t>QT220-2_OK</t>
-  </si>
-  <si>
-    <t>N/F</t>
-  </si>
-  <si>
-    <t>NOT FOUND IN DB</t>
-  </si>
-  <si>
-    <t>eWON</t>
-  </si>
-  <si>
-    <t>eWON Talk2M STATUS</t>
-  </si>
-  <si>
-    <t>LA201-1</t>
-  </si>
-  <si>
-    <t>INLET SIGHT GLASS BACKLIGHT</t>
-  </si>
-  <si>
-    <t>LA220-1</t>
-  </si>
-  <si>
-    <t>OUTLET SIGHT GLASS BACKLIGHT</t>
-  </si>
-  <si>
-    <t>L-GN</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-GREEN LIGHT</t>
-  </si>
-  <si>
-    <t>L-YL</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-YELLOW LIGHT</t>
-  </si>
-  <si>
-    <t>L-RD</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-RED LIGHT/ALARM LIGHT</t>
-  </si>
-  <si>
-    <t>L-BUZZ</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-BUZZIER</t>
-  </si>
-  <si>
-    <t>LA221-1</t>
-  </si>
-  <si>
-    <t>PIT201-1</t>
-  </si>
-  <si>
-    <t>INLET PRESSURE</t>
-  </si>
-  <si>
-    <t>PIT22X-1</t>
-  </si>
-  <si>
-    <t>SEPARATOR OUTLET 220 PRESSURE</t>
-  </si>
-  <si>
-    <t>QT201-1</t>
-  </si>
-  <si>
-    <t>INLET TURBIDITY</t>
-  </si>
-  <si>
-    <t>QT220-1</t>
-  </si>
-  <si>
-    <t>OUTLET TURBIDITY</t>
-  </si>
-  <si>
-    <t>QT220-2</t>
-  </si>
-  <si>
-    <t>PIT22Y-1</t>
-  </si>
-  <si>
-    <t>SEPARATOR OUTLET 221 PRESSURE</t>
-  </si>
-  <si>
-    <t>PIT222-1</t>
-  </si>
-  <si>
-    <t>SOLIDS OUTLET PRESSURE</t>
-  </si>
-  <si>
-    <t>LT-BT</t>
-  </si>
-  <si>
-    <t>BUFFER TANK LEVEL</t>
-  </si>
-  <si>
-    <t>LT463-1</t>
-  </si>
-  <si>
-    <t>LEVEL IN B463-1</t>
-  </si>
-  <si>
-    <t>PIT463-1</t>
-  </si>
-  <si>
-    <t>E-MOTION PRESSURE</t>
-  </si>
-  <si>
-    <t>TT406-1</t>
-  </si>
-  <si>
-    <t>COOLING LIQUID TEMPERATURE</t>
-  </si>
-  <si>
-    <t>EM - 430</t>
-  </si>
-  <si>
-    <t>FIT201-1</t>
-  </si>
-  <si>
-    <t>FEED FLOW</t>
-  </si>
-  <si>
-    <t>FIT208-1</t>
-  </si>
-  <si>
-    <t>BLENDING FLOW</t>
-  </si>
-  <si>
-    <t>FIT409-1</t>
-  </si>
-  <si>
-    <t>FCV201-1</t>
-  </si>
-  <si>
-    <t>PCV22X-1</t>
-  </si>
-  <si>
-    <t>BACK PRESSURE 220</t>
-  </si>
-  <si>
-    <t>IP506A</t>
-  </si>
-  <si>
-    <t>DISCHARGE PRESSURE</t>
-  </si>
-  <si>
-    <t>PCV22Y-1</t>
-  </si>
-  <si>
-    <t>BACK PRESSURE 221</t>
-  </si>
-  <si>
-    <t>FCV208-1</t>
-  </si>
-  <si>
-    <t>FCV210-1</t>
-  </si>
-  <si>
-    <t>RECIRCULATION FLOW</t>
-  </si>
-  <si>
-    <t>FCV430-1</t>
-  </si>
-  <si>
-    <t>GLYCOL FLOW</t>
-  </si>
-  <si>
-    <t>FCV409-1</t>
-  </si>
-  <si>
-    <t>COOLING LIQUID FLOW CONTROL VALVE</t>
-  </si>
-  <si>
-    <t>ST74X</t>
-  </si>
-  <si>
-    <t>SPEED SENSOR PULSES</t>
-  </si>
-  <si>
-    <t>ST749</t>
-  </si>
-  <si>
-    <t>SPEED SENSOR ALFDEX</t>
-  </si>
-  <si>
-    <t>EMS</t>
-  </si>
-  <si>
-    <t>E-STOP</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>UPS BATTERY</t>
-  </si>
-  <si>
-    <t>P+F OS</t>
-  </si>
-  <si>
-    <t>OVERSPEED</t>
-  </si>
-  <si>
-    <t>EM - 740</t>
-  </si>
-  <si>
-    <t>P+F ERROR</t>
-  </si>
-  <si>
-    <t>ERROR</t>
-  </si>
-  <si>
-    <t>TS222-1</t>
-  </si>
-  <si>
-    <t>SOLIDS PUMP TEMPERATURE</t>
-  </si>
-  <si>
-    <t>UPDATE: EXIST: DB=False-&gt;True</t>
-  </si>
-  <si>
-    <t>TS730</t>
-  </si>
-  <si>
-    <t>MOTOR WINDINGS TEMPERATURE</t>
-  </si>
-  <si>
-    <t>EM - 730</t>
-  </si>
-  <si>
-    <t>UPDATE: ENABLE: DB=True-&gt;False, EXIST: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>LS222-1</t>
-  </si>
-  <si>
-    <t>HIGH-HIGH LEVEL IN CYCLONE</t>
-  </si>
-  <si>
-    <t>LS222-2</t>
-  </si>
-  <si>
-    <t>HIGH LEVEL IN CYCLONE</t>
-  </si>
-  <si>
-    <t>LS222-3</t>
-  </si>
-  <si>
-    <t>LOW LEVEL IN CYCLONE</t>
-  </si>
-  <si>
-    <t>M701</t>
-  </si>
-  <si>
-    <t>SEPARATOR VFD TRIP FB</t>
-  </si>
-  <si>
-    <t>EM - 701</t>
-  </si>
-  <si>
-    <t>P222-1</t>
-  </si>
-  <si>
-    <t>SOLIDS PUMP RUN FB</t>
-  </si>
-  <si>
-    <t>P403-1</t>
-  </si>
-  <si>
-    <t>OIL COOLING PUMP RUN FB</t>
-  </si>
-  <si>
-    <t>EM - 420</t>
-  </si>
-  <si>
-    <t>P406-1</t>
-  </si>
-  <si>
-    <t>COOLING RECIRC PUMP RUN FB</t>
   </si>
   <si>
     <t>P463-1</t>
@@ -1954,14 +1960,14 @@
       <c r="E5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>26</v>
+      <c r="F5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>32</v>
@@ -1981,14 +1987,14 @@
       <c r="N5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="5" t="s">
-        <v>26</v>
+      <c r="O5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>32</v>
@@ -2008,14 +2014,14 @@
       <c r="W5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X5" s="5" t="s">
-        <v>26</v>
+      <c r="X5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA5" s="4" t="s">
         <v>32</v>
@@ -2035,14 +2041,14 @@
       <c r="AF5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG5" s="5" t="s">
-        <v>26</v>
+      <c r="AG5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AJ5" s="4" t="s">
         <v>32</v>
@@ -2062,14 +2068,14 @@
       <c r="AO5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP5" s="5" t="s">
-        <v>26</v>
+      <c r="AP5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AR5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS5" s="4" t="s">
         <v>32</v>
@@ -2089,14 +2095,14 @@
       <c r="AX5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY5" s="5" t="s">
-        <v>26</v>
+      <c r="AY5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BA5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB5" s="4" t="s">
         <v>32</v>
@@ -2116,14 +2122,14 @@
       <c r="BG5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH5" s="5" t="s">
-        <v>26</v>
+      <c r="BH5" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BJ5" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BK5" s="4" t="s">
         <v>32</v>
@@ -2157,14 +2163,14 @@
       <c r="E6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>26</v>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>32</v>
@@ -2184,14 +2190,14 @@
       <c r="N6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="5" t="s">
-        <v>26</v>
+      <c r="O6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>32</v>
@@ -2211,14 +2217,14 @@
       <c r="W6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X6" s="5" t="s">
-        <v>26</v>
+      <c r="X6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA6" s="4" t="s">
         <v>32</v>
@@ -2238,14 +2244,14 @@
       <c r="AF6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG6" s="5" t="s">
-        <v>26</v>
+      <c r="AG6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AJ6" s="4" t="s">
         <v>32</v>
@@ -2265,14 +2271,14 @@
       <c r="AO6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP6" s="5" t="s">
-        <v>26</v>
+      <c r="AP6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AR6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS6" s="4" t="s">
         <v>32</v>
@@ -2292,14 +2298,14 @@
       <c r="AX6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY6" s="5" t="s">
-        <v>26</v>
+      <c r="AY6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BA6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB6" s="4" t="s">
         <v>32</v>
@@ -2319,14 +2325,14 @@
       <c r="BG6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH6" s="5" t="s">
-        <v>26</v>
+      <c r="BH6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BJ6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BK6" s="4" t="s">
         <v>32</v>
@@ -2758,13 +2764,13 @@
         <v>22</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>32</v>
@@ -2788,10 +2794,10 @@
         <v>33</v>
       </c>
       <c r="M9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>32</v>
@@ -2815,10 +2821,10 @@
         <v>33</v>
       </c>
       <c r="V9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="X9" s="4" t="s">
         <v>32</v>
@@ -2842,10 +2848,10 @@
         <v>33</v>
       </c>
       <c r="AE9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AF9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AG9" s="4" t="s">
         <v>32</v>
@@ -2869,10 +2875,10 @@
         <v>33</v>
       </c>
       <c r="AN9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AO9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AP9" s="4" t="s">
         <v>32</v>
@@ -2896,10 +2902,10 @@
         <v>33</v>
       </c>
       <c r="AW9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AX9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AX9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AY9" s="4" t="s">
         <v>32</v>
@@ -2923,10 +2929,10 @@
         <v>33</v>
       </c>
       <c r="BF9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="BG9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="BH9" s="4" t="s">
         <v>32</v>
@@ -2950,7 +2956,7 @@
         <v>33</v>
       </c>
       <c r="BO9" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:67">
@@ -4388,7 +4394,7 @@
         <v>59</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>32</v>
@@ -4412,7 +4418,7 @@
         <v>33</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>25</v>
@@ -4794,7 +4800,7 @@
         <v>63</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>32</v>
@@ -4818,19 +4824,19 @@
         <v>33</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O19" s="5" t="s">
-        <v>26</v>
+      <c r="O19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R19" s="4" t="s">
         <v>32</v>
@@ -4850,14 +4856,14 @@
       <c r="W19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X19" s="5" t="s">
-        <v>26</v>
+      <c r="X19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA19" s="4" t="s">
         <v>32</v>
@@ -4877,14 +4883,14 @@
       <c r="AF19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG19" s="5" t="s">
-        <v>26</v>
+      <c r="AG19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AJ19" s="4" t="s">
         <v>32</v>
@@ -4904,14 +4910,14 @@
       <c r="AO19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP19" s="5" t="s">
-        <v>26</v>
+      <c r="AP19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AR19" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS19" s="4" t="s">
         <v>32</v>
@@ -4931,14 +4937,14 @@
       <c r="AX19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY19" s="5" t="s">
-        <v>26</v>
+      <c r="AY19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BA19" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB19" s="4" t="s">
         <v>32</v>
@@ -4958,14 +4964,14 @@
       <c r="BG19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH19" s="5" t="s">
-        <v>26</v>
+      <c r="BH19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BJ19" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BK19" s="4" t="s">
         <v>32</v>
@@ -4997,7 +5003,7 @@
         <v>63</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>32</v>
@@ -5021,19 +5027,19 @@
         <v>33</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="5" t="s">
-        <v>26</v>
+      <c r="O20" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R20" s="4" t="s">
         <v>32</v>
@@ -5053,14 +5059,14 @@
       <c r="W20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X20" s="5" t="s">
-        <v>26</v>
+      <c r="X20" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA20" s="4" t="s">
         <v>32</v>
@@ -5080,14 +5086,14 @@
       <c r="AF20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG20" s="5" t="s">
-        <v>26</v>
+      <c r="AG20" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AI20" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AJ20" s="4" t="s">
         <v>32</v>
@@ -5107,14 +5113,14 @@
       <c r="AO20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP20" s="5" t="s">
-        <v>26</v>
+      <c r="AP20" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AR20" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS20" s="4" t="s">
         <v>32</v>
@@ -5134,14 +5140,14 @@
       <c r="AX20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY20" s="5" t="s">
-        <v>26</v>
+      <c r="AY20" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BA20" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB20" s="4" t="s">
         <v>32</v>
@@ -5161,14 +5167,14 @@
       <c r="BG20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH20" s="5" t="s">
-        <v>26</v>
+      <c r="BH20" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="BJ20" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BK20" s="4" t="s">
         <v>32</v>
@@ -5194,13 +5200,13 @@
         <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>32</v>
@@ -5224,10 +5230,10 @@
         <v>33</v>
       </c>
       <c r="M21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>32</v>
@@ -5251,10 +5257,10 @@
         <v>33</v>
       </c>
       <c r="V21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="X21" s="4" t="s">
         <v>32</v>
@@ -5278,10 +5284,10 @@
         <v>33</v>
       </c>
       <c r="AE21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AF21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AG21" s="4" t="s">
         <v>32</v>
@@ -5305,10 +5311,10 @@
         <v>33</v>
       </c>
       <c r="AN21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AO21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AP21" s="4" t="s">
         <v>32</v>
@@ -5332,10 +5338,10 @@
         <v>33</v>
       </c>
       <c r="AW21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AX21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AX21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AY21" s="4" t="s">
         <v>32</v>
@@ -5359,10 +5365,10 @@
         <v>33</v>
       </c>
       <c r="BF21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="BG21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="BH21" s="4" t="s">
         <v>32</v>
@@ -5386,7 +5392,7 @@
         <v>33</v>
       </c>
       <c r="BO21" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:67">
@@ -5403,7 +5409,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>32</v>
@@ -5430,7 +5436,7 @@
         <v>67</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>32</v>
@@ -5457,7 +5463,7 @@
         <v>67</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X22" s="4" t="s">
         <v>32</v>
@@ -5484,7 +5490,7 @@
         <v>67</v>
       </c>
       <c r="AF22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG22" s="4" t="s">
         <v>32</v>
@@ -5511,7 +5517,7 @@
         <v>67</v>
       </c>
       <c r="AO22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP22" s="4" t="s">
         <v>32</v>
@@ -5538,7 +5544,7 @@
         <v>67</v>
       </c>
       <c r="AX22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY22" s="4" t="s">
         <v>32</v>
@@ -5565,7 +5571,7 @@
         <v>67</v>
       </c>
       <c r="BG22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH22" s="4" t="s">
         <v>32</v>
@@ -6215,7 +6221,7 @@
         <v>73</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>32</v>
@@ -6242,7 +6248,7 @@
         <v>77</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>32</v>
@@ -6269,7 +6275,7 @@
         <v>77</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X26" s="4" t="s">
         <v>32</v>
@@ -6296,7 +6302,7 @@
         <v>77</v>
       </c>
       <c r="AF26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG26" s="4" t="s">
         <v>32</v>
@@ -6323,7 +6329,7 @@
         <v>77</v>
       </c>
       <c r="AO26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP26" s="4" t="s">
         <v>32</v>
@@ -6350,7 +6356,7 @@
         <v>77</v>
       </c>
       <c r="AX26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY26" s="4" t="s">
         <v>32</v>
@@ -6377,7 +6383,7 @@
         <v>77</v>
       </c>
       <c r="BG26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH26" s="4" t="s">
         <v>32</v>
@@ -7335,7 +7341,7 @@
         <v>33</v>
       </c>
       <c r="AN31" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AO31" s="6" t="s">
         <v>31</v>
@@ -7421,7 +7427,7 @@
     </row>
     <row r="32" spans="1:67">
       <c r="A32" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>87</v>
@@ -7435,8 +7441,8 @@
       <c r="E32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>26</v>
+      <c r="F32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>32</v>
@@ -7453,8 +7459,8 @@
       <c r="K32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L32" s="6" t="s">
-        <v>90</v>
+      <c r="L32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>91</v>
@@ -7462,8 +7468,8 @@
       <c r="N32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O32" s="5" t="s">
-        <v>26</v>
+      <c r="O32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P32" s="4" t="s">
         <v>32</v>
@@ -7480,8 +7486,8 @@
       <c r="T32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U32" s="6" t="s">
-        <v>90</v>
+      <c r="U32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="V32" s="6" t="s">
         <v>91</v>
@@ -7489,8 +7495,8 @@
       <c r="W32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X32" s="5" t="s">
-        <v>26</v>
+      <c r="X32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y32" s="4" t="s">
         <v>32</v>
@@ -7507,8 +7513,8 @@
       <c r="AC32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD32" s="6" t="s">
-        <v>90</v>
+      <c r="AD32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AE32" s="6" t="s">
         <v>91</v>
@@ -7516,8 +7522,8 @@
       <c r="AF32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG32" s="5" t="s">
-        <v>26</v>
+      <c r="AG32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH32" s="4" t="s">
         <v>32</v>
@@ -7534,8 +7540,8 @@
       <c r="AL32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM32" s="6" t="s">
-        <v>90</v>
+      <c r="AM32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AN32" s="6" t="s">
         <v>91</v>
@@ -7543,8 +7549,8 @@
       <c r="AO32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP32" s="5" t="s">
-        <v>26</v>
+      <c r="AP32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ32" s="4" t="s">
         <v>32</v>
@@ -7561,8 +7567,8 @@
       <c r="AU32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV32" s="6" t="s">
-        <v>90</v>
+      <c r="AV32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AW32" s="6" t="s">
         <v>91</v>
@@ -7570,8 +7576,8 @@
       <c r="AX32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY32" s="5" t="s">
-        <v>26</v>
+      <c r="AY32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ32" s="4" t="s">
         <v>32</v>
@@ -7588,8 +7594,8 @@
       <c r="BD32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE32" s="6" t="s">
-        <v>90</v>
+      <c r="BE32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BF32" s="6" t="s">
         <v>91</v>
@@ -7597,8 +7603,8 @@
       <c r="BG32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH32" s="5" t="s">
-        <v>26</v>
+      <c r="BH32" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI32" s="4" t="s">
         <v>32</v>
@@ -7615,8 +7621,8 @@
       <c r="BM32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN32" s="6" t="s">
-        <v>90</v>
+      <c r="BN32" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BO32" s="6" t="s">
         <v>91</v>
@@ -7657,7 +7663,7 @@
         <v>66</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>67</v>
@@ -7684,7 +7690,7 @@
         <v>66</v>
       </c>
       <c r="U33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V33" s="6" t="s">
         <v>67</v>
@@ -7711,7 +7717,7 @@
         <v>66</v>
       </c>
       <c r="AD33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE33" s="6" t="s">
         <v>67</v>
@@ -7738,7 +7744,7 @@
         <v>66</v>
       </c>
       <c r="AM33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN33" s="6" t="s">
         <v>67</v>
@@ -7765,7 +7771,7 @@
         <v>66</v>
       </c>
       <c r="AV33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW33" s="6" t="s">
         <v>67</v>
@@ -7792,7 +7798,7 @@
         <v>66</v>
       </c>
       <c r="BE33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF33" s="6" t="s">
         <v>67</v>
@@ -7819,7 +7825,7 @@
         <v>66</v>
       </c>
       <c r="BN33" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO33" s="6" t="s">
         <v>67</v>
@@ -7827,10 +7833,10 @@
     </row>
     <row r="34" spans="1:67">
       <c r="A34" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>23</v>
@@ -8030,10 +8036,10 @@
     </row>
     <row r="35" spans="1:67">
       <c r="A35" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>23</v>
@@ -8233,10 +8239,10 @@
     </row>
     <row r="36" spans="1:67">
       <c r="A36" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>66</v>
@@ -8266,7 +8272,7 @@
         <v>66</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>67</v>
@@ -8293,7 +8299,7 @@
         <v>66</v>
       </c>
       <c r="U36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V36" s="6" t="s">
         <v>67</v>
@@ -8320,7 +8326,7 @@
         <v>66</v>
       </c>
       <c r="AD36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE36" s="6" t="s">
         <v>67</v>
@@ -8347,7 +8353,7 @@
         <v>66</v>
       </c>
       <c r="AM36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN36" s="6" t="s">
         <v>67</v>
@@ -8374,7 +8380,7 @@
         <v>66</v>
       </c>
       <c r="AV36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW36" s="6" t="s">
         <v>67</v>
@@ -8401,7 +8407,7 @@
         <v>66</v>
       </c>
       <c r="BE36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF36" s="6" t="s">
         <v>67</v>
@@ -8428,7 +8434,7 @@
         <v>66</v>
       </c>
       <c r="BN36" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO36" s="6" t="s">
         <v>67</v>
@@ -8436,10 +8442,10 @@
     </row>
     <row r="37" spans="1:67">
       <c r="A37" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>66</v>
@@ -8469,7 +8475,7 @@
         <v>66</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>67</v>
@@ -8496,7 +8502,7 @@
         <v>66</v>
       </c>
       <c r="U37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V37" s="6" t="s">
         <v>67</v>
@@ -8523,7 +8529,7 @@
         <v>66</v>
       </c>
       <c r="AD37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE37" s="6" t="s">
         <v>67</v>
@@ -8550,7 +8556,7 @@
         <v>66</v>
       </c>
       <c r="AM37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN37" s="6" t="s">
         <v>67</v>
@@ -8577,7 +8583,7 @@
         <v>66</v>
       </c>
       <c r="AV37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW37" s="6" t="s">
         <v>67</v>
@@ -8604,7 +8610,7 @@
         <v>66</v>
       </c>
       <c r="BE37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF37" s="6" t="s">
         <v>67</v>
@@ -8631,7 +8637,7 @@
         <v>66</v>
       </c>
       <c r="BN37" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO37" s="6" t="s">
         <v>67</v>
@@ -8639,10 +8645,10 @@
     </row>
     <row r="38" spans="1:67">
       <c r="A38" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>66</v>
@@ -8672,7 +8678,7 @@
         <v>66</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>67</v>
@@ -8699,7 +8705,7 @@
         <v>66</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V38" s="6" t="s">
         <v>67</v>
@@ -8726,7 +8732,7 @@
         <v>66</v>
       </c>
       <c r="AD38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE38" s="6" t="s">
         <v>67</v>
@@ -8753,7 +8759,7 @@
         <v>66</v>
       </c>
       <c r="AM38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN38" s="6" t="s">
         <v>67</v>
@@ -8780,7 +8786,7 @@
         <v>66</v>
       </c>
       <c r="AV38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW38" s="6" t="s">
         <v>67</v>
@@ -8807,7 +8813,7 @@
         <v>66</v>
       </c>
       <c r="BE38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF38" s="6" t="s">
         <v>67</v>
@@ -8834,7 +8840,7 @@
         <v>66</v>
       </c>
       <c r="BN38" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO38" s="6" t="s">
         <v>67</v>
@@ -8842,10 +8848,10 @@
     </row>
     <row r="39" spans="1:67">
       <c r="A39" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>58</v>
@@ -9045,19 +9051,19 @@
     </row>
     <row r="40" spans="1:67">
       <c r="A40" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>32</v>
@@ -9084,7 +9090,7 @@
         <v>77</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>32</v>
@@ -9111,7 +9117,7 @@
         <v>77</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X40" s="4" t="s">
         <v>32</v>
@@ -9138,7 +9144,7 @@
         <v>77</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG40" s="4" t="s">
         <v>32</v>
@@ -9165,7 +9171,7 @@
         <v>77</v>
       </c>
       <c r="AO40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP40" s="4" t="s">
         <v>32</v>
@@ -9192,7 +9198,7 @@
         <v>77</v>
       </c>
       <c r="AX40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY40" s="4" t="s">
         <v>32</v>
@@ -9219,7 +9225,7 @@
         <v>77</v>
       </c>
       <c r="BG40" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH40" s="4" t="s">
         <v>32</v>
@@ -9248,10 +9254,10 @@
     </row>
     <row r="41" spans="1:67">
       <c r="A41" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>23</v>
@@ -9451,10 +9457,10 @@
     </row>
     <row r="42" spans="1:67">
       <c r="A42" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
@@ -9654,10 +9660,10 @@
     </row>
     <row r="43" spans="1:67">
       <c r="A43" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>23</v>
@@ -9857,10 +9863,10 @@
     </row>
     <row r="44" spans="1:67">
       <c r="A44" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>23</v>
@@ -10060,10 +10066,10 @@
     </row>
     <row r="45" spans="1:67">
       <c r="A45" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>29</v>
@@ -10074,8 +10080,8 @@
       <c r="E45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>26</v>
+      <c r="F45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>32</v>
@@ -10092,17 +10098,17 @@
       <c r="K45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M45" s="7" t="s">
-        <v>34</v>
+      <c r="L45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O45" s="5" t="s">
-        <v>26</v>
+      <c r="O45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P45" s="4" t="s">
         <v>32</v>
@@ -10119,17 +10125,17 @@
       <c r="T45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="V45" s="7" t="s">
-        <v>34</v>
+      <c r="U45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V45" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="W45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X45" s="5" t="s">
-        <v>26</v>
+      <c r="X45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y45" s="4" t="s">
         <v>32</v>
@@ -10146,17 +10152,17 @@
       <c r="AC45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE45" s="7" t="s">
-        <v>34</v>
+      <c r="AD45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE45" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AF45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG45" s="5" t="s">
-        <v>26</v>
+      <c r="AG45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH45" s="4" t="s">
         <v>32</v>
@@ -10173,17 +10179,17 @@
       <c r="AL45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN45" s="7" t="s">
-        <v>34</v>
+      <c r="AM45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN45" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AO45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP45" s="5" t="s">
-        <v>26</v>
+      <c r="AP45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ45" s="4" t="s">
         <v>32</v>
@@ -10200,17 +10206,17 @@
       <c r="AU45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW45" s="7" t="s">
-        <v>34</v>
+      <c r="AV45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW45" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AX45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY45" s="5" t="s">
-        <v>26</v>
+      <c r="AY45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ45" s="4" t="s">
         <v>32</v>
@@ -10227,17 +10233,17 @@
       <c r="BD45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF45" s="7" t="s">
-        <v>34</v>
+      <c r="BE45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF45" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BG45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH45" s="5" t="s">
-        <v>26</v>
+      <c r="BH45" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI45" s="4" t="s">
         <v>32</v>
@@ -10254,28 +10260,28 @@
       <c r="BM45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO45" s="7" t="s">
-        <v>34</v>
+      <c r="BN45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO45" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:67">
       <c r="A46" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>32</v>
@@ -10302,7 +10308,7 @@
         <v>77</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>32</v>
@@ -10329,7 +10335,7 @@
         <v>77</v>
       </c>
       <c r="W46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X46" s="4" t="s">
         <v>32</v>
@@ -10356,7 +10362,7 @@
         <v>77</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG46" s="4" t="s">
         <v>32</v>
@@ -10383,7 +10389,7 @@
         <v>77</v>
       </c>
       <c r="AO46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP46" s="4" t="s">
         <v>32</v>
@@ -10410,7 +10416,7 @@
         <v>77</v>
       </c>
       <c r="AX46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY46" s="4" t="s">
         <v>32</v>
@@ -10437,7 +10443,7 @@
         <v>77</v>
       </c>
       <c r="BG46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH46" s="4" t="s">
         <v>32</v>
@@ -10466,10 +10472,10 @@
     </row>
     <row r="47" spans="1:67">
       <c r="A47" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>47</v>
@@ -10478,7 +10484,7 @@
         <v>48</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>32</v>
@@ -10505,7 +10511,7 @@
         <v>27</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O47" s="4" t="s">
         <v>32</v>
@@ -10532,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="W47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X47" s="4" t="s">
         <v>32</v>
@@ -10559,7 +10565,7 @@
         <v>27</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG47" s="4" t="s">
         <v>32</v>
@@ -10586,7 +10592,7 @@
         <v>27</v>
       </c>
       <c r="AO47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP47" s="4" t="s">
         <v>32</v>
@@ -10613,7 +10619,7 @@
         <v>27</v>
       </c>
       <c r="AX47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY47" s="4" t="s">
         <v>32</v>
@@ -10669,10 +10675,10 @@
     </row>
     <row r="48" spans="1:67">
       <c r="A48" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>66</v>
@@ -10702,7 +10708,7 @@
         <v>66</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>67</v>
@@ -10729,7 +10735,7 @@
         <v>66</v>
       </c>
       <c r="U48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V48" s="6" t="s">
         <v>67</v>
@@ -10756,7 +10762,7 @@
         <v>66</v>
       </c>
       <c r="AD48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE48" s="6" t="s">
         <v>67</v>
@@ -10783,7 +10789,7 @@
         <v>66</v>
       </c>
       <c r="AM48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN48" s="6" t="s">
         <v>67</v>
@@ -10810,7 +10816,7 @@
         <v>66</v>
       </c>
       <c r="AV48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW48" s="6" t="s">
         <v>67</v>
@@ -10837,7 +10843,7 @@
         <v>66</v>
       </c>
       <c r="BE48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF48" s="6" t="s">
         <v>67</v>
@@ -10864,7 +10870,7 @@
         <v>66</v>
       </c>
       <c r="BN48" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO48" s="6" t="s">
         <v>67</v>
@@ -10872,10 +10878,10 @@
     </row>
     <row r="49" spans="1:67">
       <c r="A49" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>29</v>
@@ -10884,7 +10890,7 @@
         <v>63</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>32</v>
@@ -10913,8 +10919,8 @@
       <c r="N49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O49" s="5" t="s">
-        <v>26</v>
+      <c r="O49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P49" s="4" t="s">
         <v>32</v>
@@ -10931,17 +10937,17 @@
       <c r="T49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="V49" s="7" t="s">
-        <v>34</v>
+      <c r="U49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V49" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="W49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X49" s="5" t="s">
-        <v>26</v>
+      <c r="X49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y49" s="4" t="s">
         <v>32</v>
@@ -10958,17 +10964,17 @@
       <c r="AC49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE49" s="7" t="s">
-        <v>34</v>
+      <c r="AD49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE49" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AF49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG49" s="5" t="s">
-        <v>26</v>
+      <c r="AG49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH49" s="4" t="s">
         <v>32</v>
@@ -10985,17 +10991,17 @@
       <c r="AL49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN49" s="7" t="s">
-        <v>34</v>
+      <c r="AM49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN49" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AO49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP49" s="5" t="s">
-        <v>26</v>
+      <c r="AP49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ49" s="4" t="s">
         <v>32</v>
@@ -11012,17 +11018,17 @@
       <c r="AU49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW49" s="7" t="s">
-        <v>34</v>
+      <c r="AV49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW49" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AX49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY49" s="5" t="s">
-        <v>26</v>
+      <c r="AY49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ49" s="4" t="s">
         <v>32</v>
@@ -11039,17 +11045,17 @@
       <c r="BD49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF49" s="7" t="s">
-        <v>34</v>
+      <c r="BE49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF49" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BG49" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH49" s="5" t="s">
-        <v>26</v>
+      <c r="BH49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI49" s="4" t="s">
         <v>32</v>
@@ -11066,19 +11072,19 @@
       <c r="BM49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO49" s="7" t="s">
-        <v>34</v>
+      <c r="BN49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO49" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:67">
       <c r="A50" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>29</v>
@@ -11087,7 +11093,7 @@
         <v>63</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>32</v>
@@ -11116,8 +11122,8 @@
       <c r="N50" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O50" s="5" t="s">
-        <v>26</v>
+      <c r="O50" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P50" s="4" t="s">
         <v>32</v>
@@ -11134,17 +11140,17 @@
       <c r="T50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="V50" s="7" t="s">
-        <v>34</v>
+      <c r="U50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V50" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="W50" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X50" s="5" t="s">
-        <v>26</v>
+      <c r="X50" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y50" s="4" t="s">
         <v>32</v>
@@ -11161,17 +11167,17 @@
       <c r="AC50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE50" s="7" t="s">
-        <v>34</v>
+      <c r="AD50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE50" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AF50" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG50" s="5" t="s">
-        <v>26</v>
+      <c r="AG50" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH50" s="4" t="s">
         <v>32</v>
@@ -11188,17 +11194,17 @@
       <c r="AL50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN50" s="7" t="s">
-        <v>34</v>
+      <c r="AM50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN50" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AO50" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP50" s="5" t="s">
-        <v>26</v>
+      <c r="AP50" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ50" s="4" t="s">
         <v>32</v>
@@ -11215,17 +11221,17 @@
       <c r="AU50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW50" s="7" t="s">
-        <v>34</v>
+      <c r="AV50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW50" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AX50" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY50" s="5" t="s">
-        <v>26</v>
+      <c r="AY50" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ50" s="4" t="s">
         <v>32</v>
@@ -11242,17 +11248,17 @@
       <c r="BD50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF50" s="7" t="s">
-        <v>34</v>
+      <c r="BE50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF50" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BG50" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH50" s="5" t="s">
-        <v>26</v>
+      <c r="BH50" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI50" s="4" t="s">
         <v>32</v>
@@ -11269,25 +11275,25 @@
       <c r="BM50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO50" s="7" t="s">
-        <v>34</v>
+      <c r="BN50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO50" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:67">
       <c r="A51" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>31</v>
@@ -11314,7 +11320,7 @@
         <v>33</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>31</v>
@@ -11341,7 +11347,7 @@
         <v>33</v>
       </c>
       <c r="V51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="W51" s="6" t="s">
         <v>31</v>
@@ -11368,7 +11374,7 @@
         <v>33</v>
       </c>
       <c r="AE51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AF51" s="6" t="s">
         <v>31</v>
@@ -11395,7 +11401,7 @@
         <v>33</v>
       </c>
       <c r="AN51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AO51" s="6" t="s">
         <v>31</v>
@@ -11422,7 +11428,7 @@
         <v>33</v>
       </c>
       <c r="AW51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AX51" s="6" t="s">
         <v>31</v>
@@ -11449,7 +11455,7 @@
         <v>33</v>
       </c>
       <c r="BF51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="BG51" s="6" t="s">
         <v>31</v>
@@ -11476,15 +11482,15 @@
         <v>33</v>
       </c>
       <c r="BO51" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:67">
       <c r="A52" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>23</v>
@@ -11684,10 +11690,10 @@
     </row>
     <row r="53" spans="1:67">
       <c r="A53" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>29</v>
@@ -11698,8 +11704,8 @@
       <c r="E53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>26</v>
+      <c r="F53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>32</v>
@@ -11716,17 +11722,17 @@
       <c r="K53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M53" s="7" t="s">
-        <v>34</v>
+      <c r="L53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O53" s="5" t="s">
-        <v>26</v>
+      <c r="O53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P53" s="4" t="s">
         <v>32</v>
@@ -11743,17 +11749,17 @@
       <c r="T53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="V53" s="7" t="s">
-        <v>34</v>
+      <c r="U53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V53" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="W53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X53" s="5" t="s">
-        <v>26</v>
+      <c r="X53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y53" s="4" t="s">
         <v>32</v>
@@ -11770,17 +11776,17 @@
       <c r="AC53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE53" s="7" t="s">
-        <v>34</v>
+      <c r="AD53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE53" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AF53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG53" s="5" t="s">
-        <v>26</v>
+      <c r="AG53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH53" s="4" t="s">
         <v>32</v>
@@ -11797,17 +11803,17 @@
       <c r="AL53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN53" s="7" t="s">
-        <v>34</v>
+      <c r="AM53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN53" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AO53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP53" s="5" t="s">
-        <v>26</v>
+      <c r="AP53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ53" s="4" t="s">
         <v>32</v>
@@ -11824,17 +11830,17 @@
       <c r="AU53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW53" s="7" t="s">
-        <v>34</v>
+      <c r="AV53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW53" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AX53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY53" s="5" t="s">
-        <v>26</v>
+      <c r="AY53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ53" s="4" t="s">
         <v>32</v>
@@ -11851,17 +11857,17 @@
       <c r="BD53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF53" s="7" t="s">
-        <v>34</v>
+      <c r="BE53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF53" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BG53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH53" s="5" t="s">
-        <v>26</v>
+      <c r="BH53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI53" s="4" t="s">
         <v>32</v>
@@ -11878,16 +11884,16 @@
       <c r="BM53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO53" s="7" t="s">
-        <v>34</v>
+      <c r="BN53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO53" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:67">
       <c r="A54" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>69</v>
@@ -12090,10 +12096,10 @@
     </row>
     <row r="55" spans="1:67">
       <c r="A55" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>23</v>
@@ -12293,10 +12299,10 @@
     </row>
     <row r="56" spans="1:67">
       <c r="A56" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -12496,10 +12502,10 @@
     </row>
     <row r="57" spans="1:67">
       <c r="A57" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>66</v>
@@ -12529,7 +12535,7 @@
         <v>66</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>67</v>
@@ -12556,7 +12562,7 @@
         <v>66</v>
       </c>
       <c r="U57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V57" s="6" t="s">
         <v>67</v>
@@ -12583,7 +12589,7 @@
         <v>66</v>
       </c>
       <c r="AD57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE57" s="6" t="s">
         <v>67</v>
@@ -12610,7 +12616,7 @@
         <v>66</v>
       </c>
       <c r="AM57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN57" s="6" t="s">
         <v>67</v>
@@ -12637,7 +12643,7 @@
         <v>66</v>
       </c>
       <c r="AV57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW57" s="6" t="s">
         <v>67</v>
@@ -12664,7 +12670,7 @@
         <v>66</v>
       </c>
       <c r="BE57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF57" s="6" t="s">
         <v>67</v>
@@ -12691,7 +12697,7 @@
         <v>66</v>
       </c>
       <c r="BN57" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO57" s="6" t="s">
         <v>67</v>
@@ -12699,19 +12705,19 @@
     </row>
     <row r="58" spans="1:67">
       <c r="A58" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>32</v>
@@ -12738,7 +12744,7 @@
         <v>77</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O58" s="4" t="s">
         <v>32</v>
@@ -12765,7 +12771,7 @@
         <v>77</v>
       </c>
       <c r="W58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X58" s="4" t="s">
         <v>32</v>
@@ -12792,7 +12798,7 @@
         <v>77</v>
       </c>
       <c r="AF58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG58" s="4" t="s">
         <v>32</v>
@@ -12819,7 +12825,7 @@
         <v>77</v>
       </c>
       <c r="AO58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP58" s="4" t="s">
         <v>32</v>
@@ -12846,7 +12852,7 @@
         <v>77</v>
       </c>
       <c r="AX58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY58" s="4" t="s">
         <v>32</v>
@@ -12873,7 +12879,7 @@
         <v>77</v>
       </c>
       <c r="BG58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH58" s="4" t="s">
         <v>32</v>
@@ -12902,10 +12908,10 @@
     </row>
     <row r="59" spans="1:67">
       <c r="A59" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>29</v>
@@ -12916,8 +12922,8 @@
       <c r="E59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>26</v>
+      <c r="F59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>32</v>
@@ -12934,17 +12940,17 @@
       <c r="K59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M59" s="7" t="s">
-        <v>34</v>
+      <c r="L59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O59" s="5" t="s">
-        <v>26</v>
+      <c r="O59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P59" s="4" t="s">
         <v>32</v>
@@ -12961,17 +12967,17 @@
       <c r="T59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="V59" s="7" t="s">
-        <v>34</v>
+      <c r="U59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V59" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="W59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X59" s="5" t="s">
-        <v>26</v>
+      <c r="X59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y59" s="4" t="s">
         <v>32</v>
@@ -12988,17 +12994,17 @@
       <c r="AC59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE59" s="7" t="s">
-        <v>34</v>
+      <c r="AD59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE59" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AF59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG59" s="5" t="s">
-        <v>26</v>
+      <c r="AG59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH59" s="4" t="s">
         <v>32</v>
@@ -13015,17 +13021,17 @@
       <c r="AL59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN59" s="7" t="s">
-        <v>34</v>
+      <c r="AM59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN59" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AO59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP59" s="5" t="s">
-        <v>26</v>
+      <c r="AP59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ59" s="4" t="s">
         <v>32</v>
@@ -13042,17 +13048,17 @@
       <c r="AU59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW59" s="7" t="s">
-        <v>34</v>
+      <c r="AV59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW59" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AX59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY59" s="5" t="s">
-        <v>26</v>
+      <c r="AY59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ59" s="4" t="s">
         <v>32</v>
@@ -13069,17 +13075,17 @@
       <c r="BD59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF59" s="7" t="s">
-        <v>34</v>
+      <c r="BE59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF59" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BG59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH59" s="5" t="s">
-        <v>26</v>
+      <c r="BH59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI59" s="4" t="s">
         <v>32</v>
@@ -13096,19 +13102,19 @@
       <c r="BM59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO59" s="7" t="s">
-        <v>34</v>
+      <c r="BN59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO59" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:67">
       <c r="A60" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>29</v>
@@ -13119,8 +13125,8 @@
       <c r="E60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>26</v>
+      <c r="F60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>32</v>
@@ -13137,17 +13143,17 @@
       <c r="K60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M60" s="7" t="s">
-        <v>34</v>
+      <c r="L60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O60" s="5" t="s">
-        <v>26</v>
+      <c r="O60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P60" s="4" t="s">
         <v>32</v>
@@ -13164,17 +13170,17 @@
       <c r="T60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="V60" s="7" t="s">
-        <v>34</v>
+      <c r="U60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V60" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="W60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X60" s="5" t="s">
-        <v>26</v>
+      <c r="X60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>32</v>
@@ -13191,17 +13197,17 @@
       <c r="AC60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AD60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE60" s="7" t="s">
-        <v>34</v>
+      <c r="AD60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE60" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AF60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG60" s="5" t="s">
-        <v>26</v>
+      <c r="AG60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH60" s="4" t="s">
         <v>32</v>
@@ -13218,17 +13224,17 @@
       <c r="AL60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AM60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN60" s="7" t="s">
-        <v>34</v>
+      <c r="AM60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN60" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AO60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP60" s="5" t="s">
-        <v>26</v>
+      <c r="AP60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ60" s="4" t="s">
         <v>32</v>
@@ -13245,17 +13251,17 @@
       <c r="AU60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AV60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW60" s="7" t="s">
-        <v>34</v>
+      <c r="AV60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW60" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AX60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY60" s="5" t="s">
-        <v>26</v>
+      <c r="AY60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ60" s="4" t="s">
         <v>32</v>
@@ -13272,17 +13278,17 @@
       <c r="BD60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF60" s="7" t="s">
-        <v>34</v>
+      <c r="BE60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF60" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="BG60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH60" s="5" t="s">
-        <v>26</v>
+      <c r="BH60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI60" s="4" t="s">
         <v>32</v>
@@ -13299,25 +13305,25 @@
       <c r="BM60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BN60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO60" s="7" t="s">
-        <v>34</v>
+      <c r="BN60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO60" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:67">
       <c r="A61" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>31</v>
@@ -13344,7 +13350,7 @@
         <v>33</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="N61" s="6" t="s">
         <v>31</v>
@@ -13371,7 +13377,7 @@
         <v>33</v>
       </c>
       <c r="V61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="W61" s="6" t="s">
         <v>31</v>
@@ -13398,7 +13404,7 @@
         <v>33</v>
       </c>
       <c r="AE61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AF61" s="6" t="s">
         <v>31</v>
@@ -13425,7 +13431,7 @@
         <v>33</v>
       </c>
       <c r="AN61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AO61" s="6" t="s">
         <v>31</v>
@@ -13452,7 +13458,7 @@
         <v>33</v>
       </c>
       <c r="AW61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AX61" s="6" t="s">
         <v>31</v>
@@ -13479,7 +13485,7 @@
         <v>33</v>
       </c>
       <c r="BF61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="BG61" s="6" t="s">
         <v>31</v>
@@ -13506,15 +13512,15 @@
         <v>33</v>
       </c>
       <c r="BO61" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:67">
       <c r="A62" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>58</v>
@@ -13714,10 +13720,10 @@
     </row>
     <row r="63" spans="1:67">
       <c r="A63" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>66</v>
@@ -13747,7 +13753,7 @@
         <v>66</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>67</v>
@@ -13774,7 +13780,7 @@
         <v>66</v>
       </c>
       <c r="U63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V63" s="6" t="s">
         <v>67</v>
@@ -13801,7 +13807,7 @@
         <v>66</v>
       </c>
       <c r="AD63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE63" s="6" t="s">
         <v>67</v>
@@ -13828,7 +13834,7 @@
         <v>66</v>
       </c>
       <c r="AM63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN63" s="6" t="s">
         <v>67</v>
@@ -13855,7 +13861,7 @@
         <v>66</v>
       </c>
       <c r="AV63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW63" s="6" t="s">
         <v>67</v>
@@ -13882,7 +13888,7 @@
         <v>66</v>
       </c>
       <c r="BE63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF63" s="6" t="s">
         <v>67</v>
@@ -13909,7 +13915,7 @@
         <v>66</v>
       </c>
       <c r="BN63" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO63" s="6" t="s">
         <v>67</v>
@@ -13917,10 +13923,10 @@
     </row>
     <row r="64" spans="1:67">
       <c r="A64" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>66</v>
@@ -13929,7 +13935,7 @@
         <v>66</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>32</v>
@@ -13956,7 +13962,7 @@
         <v>67</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O64" s="4" t="s">
         <v>32</v>
@@ -13983,7 +13989,7 @@
         <v>67</v>
       </c>
       <c r="W64" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X64" s="4" t="s">
         <v>32</v>
@@ -14010,7 +14016,7 @@
         <v>67</v>
       </c>
       <c r="AF64" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG64" s="4" t="s">
         <v>32</v>
@@ -14037,7 +14043,7 @@
         <v>67</v>
       </c>
       <c r="AO64" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP64" s="4" t="s">
         <v>32</v>
@@ -14064,7 +14070,7 @@
         <v>67</v>
       </c>
       <c r="AX64" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY64" s="4" t="s">
         <v>32</v>
@@ -14112,7 +14118,7 @@
         <v>66</v>
       </c>
       <c r="BN64" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO64" s="6" t="s">
         <v>67</v>
@@ -14120,10 +14126,10 @@
     </row>
     <row r="65" spans="1:67">
       <c r="A65" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>58</v>
@@ -14323,10 +14329,10 @@
     </row>
     <row r="66" spans="1:67">
       <c r="A66" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>58</v>
@@ -14526,16 +14532,16 @@
     </row>
     <row r="67" spans="1:67">
       <c r="A67" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>25</v>
@@ -14729,16 +14735,16 @@
     </row>
     <row r="68" spans="1:67">
       <c r="A68" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>25</v>
@@ -14932,10 +14938,10 @@
     </row>
     <row r="69" spans="1:67">
       <c r="A69" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>47</v>
@@ -15130,21 +15136,21 @@
         <v>33</v>
       </c>
       <c r="BO69" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:67">
       <c r="A70" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>25</v>
@@ -15255,7 +15261,7 @@
         <v>27</v>
       </c>
       <c r="AO70" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP70" s="4" t="s">
         <v>32</v>
@@ -15279,10 +15285,10 @@
         <v>33</v>
       </c>
       <c r="AW70" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AX70" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY70" s="4" t="s">
         <v>32</v>
@@ -15306,7 +15312,7 @@
         <v>33</v>
       </c>
       <c r="BF70" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BG70" s="5" t="s">
         <v>25</v>
@@ -15338,10 +15344,10 @@
     </row>
     <row r="71" spans="1:67">
       <c r="A71" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>47</v>
@@ -15541,10 +15547,10 @@
     </row>
     <row r="72" spans="1:67">
       <c r="A72" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>47</v>
@@ -15553,7 +15559,7 @@
         <v>48</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>32</v>
@@ -15580,7 +15586,7 @@
         <v>27</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O72" s="4" t="s">
         <v>32</v>
@@ -15607,7 +15613,7 @@
         <v>27</v>
       </c>
       <c r="W72" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X72" s="4" t="s">
         <v>32</v>
@@ -15634,7 +15640,7 @@
         <v>27</v>
       </c>
       <c r="AF72" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG72" s="4" t="s">
         <v>32</v>
@@ -15661,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="AO72" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP72" s="4" t="s">
         <v>32</v>
@@ -15688,7 +15694,7 @@
         <v>27</v>
       </c>
       <c r="AX72" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY72" s="4" t="s">
         <v>32</v>
@@ -15744,10 +15750,10 @@
     </row>
     <row r="73" spans="1:67">
       <c r="A73" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>47</v>
@@ -15756,7 +15762,7 @@
         <v>48</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>32</v>
@@ -15783,7 +15789,7 @@
         <v>27</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O73" s="4" t="s">
         <v>32</v>
@@ -15810,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="W73" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X73" s="4" t="s">
         <v>32</v>
@@ -15837,7 +15843,7 @@
         <v>27</v>
       </c>
       <c r="AF73" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG73" s="4" t="s">
         <v>32</v>
@@ -15864,7 +15870,7 @@
         <v>27</v>
       </c>
       <c r="AO73" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP73" s="4" t="s">
         <v>32</v>
@@ -15891,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="AX73" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY73" s="4" t="s">
         <v>32</v>
@@ -15947,16 +15953,16 @@
     </row>
     <row r="74" spans="1:67">
       <c r="A74" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>25</v>
@@ -16150,10 +16156,10 @@
     </row>
     <row r="75" spans="1:67">
       <c r="A75" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>47</v>
@@ -16353,19 +16359,19 @@
     </row>
     <row r="76" spans="1:67">
       <c r="A76" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>32</v>
@@ -16392,7 +16398,7 @@
         <v>77</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O76" s="4" t="s">
         <v>32</v>
@@ -16419,7 +16425,7 @@
         <v>77</v>
       </c>
       <c r="W76" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X76" s="4" t="s">
         <v>32</v>
@@ -16446,7 +16452,7 @@
         <v>77</v>
       </c>
       <c r="AF76" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG76" s="4" t="s">
         <v>32</v>
@@ -16527,7 +16533,7 @@
         <v>27</v>
       </c>
       <c r="BG76" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH76" s="4" t="s">
         <v>32</v>
@@ -16556,16 +16562,16 @@
     </row>
     <row r="77" spans="1:67">
       <c r="A77" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>31</v>
@@ -16592,7 +16598,7 @@
         <v>33</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="N77" s="6" t="s">
         <v>31</v>
@@ -16619,7 +16625,7 @@
         <v>33</v>
       </c>
       <c r="V77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="W77" s="6" t="s">
         <v>31</v>
@@ -16646,7 +16652,7 @@
         <v>33</v>
       </c>
       <c r="AE77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="AF77" s="6" t="s">
         <v>31</v>
@@ -16673,7 +16679,7 @@
         <v>33</v>
       </c>
       <c r="AN77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="AO77" s="6" t="s">
         <v>31</v>
@@ -16700,7 +16706,7 @@
         <v>33</v>
       </c>
       <c r="AW77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="AX77" s="6" t="s">
         <v>31</v>
@@ -16727,7 +16733,7 @@
         <v>33</v>
       </c>
       <c r="BF77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="BG77" s="6" t="s">
         <v>31</v>
@@ -16754,15 +16760,15 @@
         <v>33</v>
       </c>
       <c r="BO77" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:67">
       <c r="A78" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>29</v>
@@ -16771,7 +16777,7 @@
         <v>63</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>32</v>
@@ -16800,8 +16806,8 @@
       <c r="N78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O78" s="5" t="s">
-        <v>26</v>
+      <c r="O78" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P78" s="4" t="s">
         <v>32</v>
@@ -16822,13 +16828,13 @@
         <v>33</v>
       </c>
       <c r="V78" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X78" s="5" t="s">
-        <v>26</v>
+      <c r="X78" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y78" s="4" t="s">
         <v>32</v>
@@ -16849,13 +16855,13 @@
         <v>33</v>
       </c>
       <c r="AE78" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG78" s="5" t="s">
-        <v>26</v>
+      <c r="AG78" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH78" s="4" t="s">
         <v>32</v>
@@ -16876,13 +16882,13 @@
         <v>33</v>
       </c>
       <c r="AN78" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP78" s="5" t="s">
-        <v>26</v>
+      <c r="AP78" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ78" s="4" t="s">
         <v>32</v>
@@ -16903,13 +16909,13 @@
         <v>33</v>
       </c>
       <c r="AW78" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY78" s="5" t="s">
-        <v>26</v>
+      <c r="AY78" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ78" s="4" t="s">
         <v>32</v>
@@ -16930,13 +16936,13 @@
         <v>33</v>
       </c>
       <c r="BF78" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH78" s="5" t="s">
-        <v>26</v>
+      <c r="BH78" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI78" s="4" t="s">
         <v>32</v>
@@ -16957,27 +16963,27 @@
         <v>33</v>
       </c>
       <c r="BO78" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:67">
       <c r="A79" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F79" s="5" t="s">
-        <v>26</v>
+      <c r="F79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>32</v>
@@ -16998,13 +17004,13 @@
         <v>33</v>
       </c>
       <c r="M79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="N79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O79" s="5" t="s">
-        <v>26</v>
+      <c r="O79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P79" s="4" t="s">
         <v>32</v>
@@ -17025,13 +17031,13 @@
         <v>33</v>
       </c>
       <c r="V79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X79" s="5" t="s">
-        <v>26</v>
+      <c r="X79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y79" s="4" t="s">
         <v>32</v>
@@ -17052,13 +17058,13 @@
         <v>33</v>
       </c>
       <c r="AE79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG79" s="5" t="s">
-        <v>26</v>
+      <c r="AG79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH79" s="4" t="s">
         <v>32</v>
@@ -17079,13 +17085,13 @@
         <v>33</v>
       </c>
       <c r="AN79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP79" s="5" t="s">
-        <v>26</v>
+      <c r="AP79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ79" s="4" t="s">
         <v>32</v>
@@ -17106,13 +17112,13 @@
         <v>33</v>
       </c>
       <c r="AW79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY79" s="5" t="s">
-        <v>26</v>
+      <c r="AY79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ79" s="4" t="s">
         <v>32</v>
@@ -17133,13 +17139,13 @@
         <v>33</v>
       </c>
       <c r="BF79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH79" s="5" t="s">
-        <v>26</v>
+      <c r="BH79" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI79" s="4" t="s">
         <v>32</v>
@@ -17160,15 +17166,15 @@
         <v>33</v>
       </c>
       <c r="BO79" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:67">
       <c r="A80" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>29</v>
@@ -17179,8 +17185,8 @@
       <c r="E80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>26</v>
+      <c r="F80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>32</v>
@@ -17201,13 +17207,13 @@
         <v>33</v>
       </c>
       <c r="M80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="N80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O80" s="5" t="s">
-        <v>26</v>
+      <c r="O80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P80" s="4" t="s">
         <v>32</v>
@@ -17228,13 +17234,13 @@
         <v>33</v>
       </c>
       <c r="V80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X80" s="5" t="s">
-        <v>26</v>
+      <c r="X80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y80" s="4" t="s">
         <v>32</v>
@@ -17255,13 +17261,13 @@
         <v>33</v>
       </c>
       <c r="AE80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG80" s="5" t="s">
-        <v>26</v>
+      <c r="AG80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH80" s="4" t="s">
         <v>32</v>
@@ -17282,13 +17288,13 @@
         <v>33</v>
       </c>
       <c r="AN80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP80" s="5" t="s">
-        <v>26</v>
+      <c r="AP80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ80" s="4" t="s">
         <v>32</v>
@@ -17309,13 +17315,13 @@
         <v>33</v>
       </c>
       <c r="AW80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY80" s="5" t="s">
-        <v>26</v>
+      <c r="AY80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ80" s="4" t="s">
         <v>32</v>
@@ -17336,13 +17342,13 @@
         <v>33</v>
       </c>
       <c r="BF80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH80" s="5" t="s">
-        <v>26</v>
+      <c r="BH80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI80" s="4" t="s">
         <v>32</v>
@@ -17363,15 +17369,15 @@
         <v>33</v>
       </c>
       <c r="BO80" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:67">
       <c r="A81" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>58</v>
@@ -17380,7 +17386,7 @@
         <v>85</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>32</v>
@@ -17407,7 +17413,7 @@
         <v>27</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O81" s="4" t="s">
         <v>32</v>
@@ -17458,7 +17464,7 @@
         <v>33</v>
       </c>
       <c r="AE81" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF81" s="5" t="s">
         <v>25</v>
@@ -17485,7 +17491,7 @@
         <v>33</v>
       </c>
       <c r="AN81" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO81" s="5" t="s">
         <v>25</v>
@@ -17512,7 +17518,7 @@
         <v>33</v>
       </c>
       <c r="AW81" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AX81" s="5" t="s">
         <v>25</v>
@@ -17539,7 +17545,7 @@
         <v>33</v>
       </c>
       <c r="BF81" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG81" s="5" t="s">
         <v>25</v>
@@ -17566,15 +17572,15 @@
         <v>33</v>
       </c>
       <c r="BO81" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:67">
       <c r="A82" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>58</v>
@@ -17583,7 +17589,7 @@
         <v>85</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>32</v>
@@ -17610,7 +17616,7 @@
         <v>27</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O82" s="4" t="s">
         <v>32</v>
@@ -17661,7 +17667,7 @@
         <v>33</v>
       </c>
       <c r="AE82" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF82" s="5" t="s">
         <v>25</v>
@@ -17688,7 +17694,7 @@
         <v>33</v>
       </c>
       <c r="AN82" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO82" s="5" t="s">
         <v>25</v>
@@ -17715,7 +17721,7 @@
         <v>33</v>
       </c>
       <c r="AW82" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AX82" s="5" t="s">
         <v>25</v>
@@ -17742,7 +17748,7 @@
         <v>33</v>
       </c>
       <c r="BF82" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG82" s="5" t="s">
         <v>25</v>
@@ -17769,15 +17775,15 @@
         <v>33</v>
       </c>
       <c r="BO82" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:67">
       <c r="A83" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>58</v>
@@ -17786,7 +17792,7 @@
         <v>85</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>32</v>
@@ -17813,7 +17819,7 @@
         <v>27</v>
       </c>
       <c r="N83" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O83" s="4" t="s">
         <v>32</v>
@@ -17864,7 +17870,7 @@
         <v>33</v>
       </c>
       <c r="AE83" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF83" s="5" t="s">
         <v>25</v>
@@ -17891,7 +17897,7 @@
         <v>33</v>
       </c>
       <c r="AN83" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO83" s="5" t="s">
         <v>25</v>
@@ -17918,7 +17924,7 @@
         <v>33</v>
       </c>
       <c r="AW83" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AX83" s="5" t="s">
         <v>25</v>
@@ -17945,7 +17951,7 @@
         <v>33</v>
       </c>
       <c r="BF83" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG83" s="5" t="s">
         <v>25</v>
@@ -17972,15 +17978,15 @@
         <v>33</v>
       </c>
       <c r="BO83" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:67">
       <c r="A84" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>58</v>
@@ -17989,7 +17995,7 @@
         <v>85</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>32</v>
@@ -18016,7 +18022,7 @@
         <v>27</v>
       </c>
       <c r="N84" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O84" s="4" t="s">
         <v>32</v>
@@ -18067,7 +18073,7 @@
         <v>33</v>
       </c>
       <c r="AE84" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF84" s="5" t="s">
         <v>25</v>
@@ -18094,7 +18100,7 @@
         <v>33</v>
       </c>
       <c r="AN84" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO84" s="5" t="s">
         <v>25</v>
@@ -18121,7 +18127,7 @@
         <v>33</v>
       </c>
       <c r="AW84" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AX84" s="5" t="s">
         <v>25</v>
@@ -18148,7 +18154,7 @@
         <v>33</v>
       </c>
       <c r="BF84" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG84" s="5" t="s">
         <v>25</v>
@@ -18175,12 +18181,12 @@
         <v>33</v>
       </c>
       <c r="BO84" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:67">
       <c r="A85" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>69</v>
@@ -18192,7 +18198,7 @@
         <v>70</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>32</v>
@@ -18219,7 +18225,7 @@
         <v>77</v>
       </c>
       <c r="N85" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O85" s="4" t="s">
         <v>32</v>
@@ -18246,7 +18252,7 @@
         <v>77</v>
       </c>
       <c r="W85" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X85" s="4" t="s">
         <v>32</v>
@@ -18273,7 +18279,7 @@
         <v>77</v>
       </c>
       <c r="AF85" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG85" s="4" t="s">
         <v>32</v>
@@ -18354,7 +18360,7 @@
         <v>27</v>
       </c>
       <c r="BG85" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH85" s="4" t="s">
         <v>32</v>
@@ -18383,10 +18389,10 @@
     </row>
     <row r="86" spans="1:67">
       <c r="A86" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>66</v>
@@ -18395,7 +18401,7 @@
         <v>66</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>32</v>
@@ -18422,7 +18428,7 @@
         <v>67</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O86" s="4" t="s">
         <v>32</v>
@@ -18449,7 +18455,7 @@
         <v>67</v>
       </c>
       <c r="W86" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X86" s="4" t="s">
         <v>32</v>
@@ -18476,7 +18482,7 @@
         <v>67</v>
       </c>
       <c r="AF86" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG86" s="4" t="s">
         <v>32</v>
@@ -18524,7 +18530,7 @@
         <v>66</v>
       </c>
       <c r="AV86" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW86" s="6" t="s">
         <v>67</v>
@@ -18551,13 +18557,13 @@
         <v>66</v>
       </c>
       <c r="BE86" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF86" s="6" t="s">
         <v>67</v>
       </c>
       <c r="BG86" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH86" s="4" t="s">
         <v>32</v>
@@ -18586,10 +18592,10 @@
     </row>
     <row r="87" spans="1:67">
       <c r="A87" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>66</v>
@@ -18598,7 +18604,7 @@
         <v>66</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>32</v>
@@ -18625,7 +18631,7 @@
         <v>67</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O87" s="4" t="s">
         <v>32</v>
@@ -18652,7 +18658,7 @@
         <v>67</v>
       </c>
       <c r="W87" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X87" s="4" t="s">
         <v>32</v>
@@ -18679,7 +18685,7 @@
         <v>67</v>
       </c>
       <c r="AF87" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG87" s="4" t="s">
         <v>32</v>
@@ -18727,7 +18733,7 @@
         <v>66</v>
       </c>
       <c r="AV87" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW87" s="6" t="s">
         <v>67</v>
@@ -18754,13 +18760,13 @@
         <v>66</v>
       </c>
       <c r="BE87" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF87" s="6" t="s">
         <v>67</v>
       </c>
       <c r="BG87" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH87" s="4" t="s">
         <v>32</v>
@@ -18789,19 +18795,19 @@
     </row>
     <row r="88" spans="1:67">
       <c r="A88" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>32</v>
@@ -18828,7 +18834,7 @@
         <v>77</v>
       </c>
       <c r="N88" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O88" s="4" t="s">
         <v>32</v>
@@ -18855,7 +18861,7 @@
         <v>77</v>
       </c>
       <c r="W88" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X88" s="4" t="s">
         <v>32</v>
@@ -18882,7 +18888,7 @@
         <v>77</v>
       </c>
       <c r="AF88" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG88" s="4" t="s">
         <v>32</v>
@@ -18963,7 +18969,7 @@
         <v>27</v>
       </c>
       <c r="BG88" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH88" s="4" t="s">
         <v>32</v>
@@ -18992,19 +18998,19 @@
     </row>
     <row r="89" spans="1:67">
       <c r="A89" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>32</v>
@@ -19031,7 +19037,7 @@
         <v>77</v>
       </c>
       <c r="N89" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O89" s="4" t="s">
         <v>32</v>
@@ -19058,7 +19064,7 @@
         <v>77</v>
       </c>
       <c r="W89" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X89" s="4" t="s">
         <v>32</v>
@@ -19085,7 +19091,7 @@
         <v>77</v>
       </c>
       <c r="AF89" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG89" s="4" t="s">
         <v>32</v>
@@ -19195,19 +19201,19 @@
     </row>
     <row r="90" spans="1:67">
       <c r="A90" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>32</v>
@@ -19234,7 +19240,7 @@
         <v>77</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O90" s="4" t="s">
         <v>32</v>
@@ -19261,7 +19267,7 @@
         <v>77</v>
       </c>
       <c r="W90" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X90" s="4" t="s">
         <v>32</v>
@@ -19288,7 +19294,7 @@
         <v>77</v>
       </c>
       <c r="AF90" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG90" s="4" t="s">
         <v>32</v>
@@ -19369,7 +19375,7 @@
         <v>27</v>
       </c>
       <c r="BG90" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH90" s="4" t="s">
         <v>32</v>
@@ -19398,10 +19404,10 @@
     </row>
     <row r="91" spans="1:67">
       <c r="A91" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>66</v>
@@ -19410,7 +19416,7 @@
         <v>66</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>32</v>
@@ -19437,7 +19443,7 @@
         <v>67</v>
       </c>
       <c r="N91" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O91" s="4" t="s">
         <v>32</v>
@@ -19464,7 +19470,7 @@
         <v>67</v>
       </c>
       <c r="W91" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X91" s="4" t="s">
         <v>32</v>
@@ -19491,7 +19497,7 @@
         <v>67</v>
       </c>
       <c r="AF91" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG91" s="4" t="s">
         <v>32</v>
@@ -19518,7 +19524,7 @@
         <v>67</v>
       </c>
       <c r="AO91" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP91" s="4" t="s">
         <v>32</v>
@@ -19545,7 +19551,7 @@
         <v>67</v>
       </c>
       <c r="AX91" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY91" s="4" t="s">
         <v>32</v>
@@ -19593,7 +19599,7 @@
         <v>66</v>
       </c>
       <c r="BN91" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO91" s="6" t="s">
         <v>67</v>
@@ -19601,16 +19607,16 @@
     </row>
     <row r="92" spans="1:67">
       <c r="A92" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>25</v>
@@ -19804,10 +19810,10 @@
     </row>
     <row r="93" spans="1:67">
       <c r="A93" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>66</v>
@@ -19837,7 +19843,7 @@
         <v>66</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>67</v>
@@ -19864,7 +19870,7 @@
         <v>66</v>
       </c>
       <c r="U93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V93" s="6" t="s">
         <v>67</v>
@@ -19891,7 +19897,7 @@
         <v>66</v>
       </c>
       <c r="AD93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE93" s="6" t="s">
         <v>67</v>
@@ -19918,7 +19924,7 @@
         <v>66</v>
       </c>
       <c r="AM93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN93" s="6" t="s">
         <v>67</v>
@@ -19945,7 +19951,7 @@
         <v>66</v>
       </c>
       <c r="AV93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW93" s="6" t="s">
         <v>67</v>
@@ -19972,7 +19978,7 @@
         <v>66</v>
       </c>
       <c r="BE93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF93" s="6" t="s">
         <v>67</v>
@@ -19999,7 +20005,7 @@
         <v>66</v>
       </c>
       <c r="BN93" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO93" s="6" t="s">
         <v>67</v>
@@ -20007,16 +20013,16 @@
     </row>
     <row r="94" spans="1:67">
       <c r="A94" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>25</v>
@@ -20210,10 +20216,10 @@
     </row>
     <row r="95" spans="1:67">
       <c r="A95" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>58</v>
@@ -20222,7 +20228,7 @@
         <v>70</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>32</v>
@@ -20249,7 +20255,7 @@
         <v>77</v>
       </c>
       <c r="N95" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O95" s="4" t="s">
         <v>32</v>
@@ -20276,7 +20282,7 @@
         <v>77</v>
       </c>
       <c r="W95" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X95" s="4" t="s">
         <v>32</v>
@@ -20300,10 +20306,10 @@
         <v>33</v>
       </c>
       <c r="AE95" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AF95" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG95" s="4" t="s">
         <v>32</v>
@@ -20327,7 +20333,7 @@
         <v>33</v>
       </c>
       <c r="AN95" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AO95" s="5" t="s">
         <v>25</v>
@@ -20384,7 +20390,7 @@
         <v>27</v>
       </c>
       <c r="BG95" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH95" s="4" t="s">
         <v>32</v>
@@ -20413,7 +20419,7 @@
     </row>
     <row r="96" spans="1:67">
       <c r="A96" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>81</v>
@@ -20425,7 +20431,7 @@
         <v>82</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>32</v>
@@ -20616,10 +20622,10 @@
     </row>
     <row r="97" spans="1:67">
       <c r="A97" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>66</v>
@@ -20628,7 +20634,7 @@
         <v>66</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>32</v>
@@ -20655,7 +20661,7 @@
         <v>67</v>
       </c>
       <c r="N97" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O97" s="4" t="s">
         <v>32</v>
@@ -20682,7 +20688,7 @@
         <v>67</v>
       </c>
       <c r="W97" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X97" s="4" t="s">
         <v>32</v>
@@ -20709,7 +20715,7 @@
         <v>67</v>
       </c>
       <c r="AF97" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG97" s="4" t="s">
         <v>32</v>
@@ -20757,7 +20763,7 @@
         <v>66</v>
       </c>
       <c r="AV97" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW97" s="6" t="s">
         <v>67</v>
@@ -20784,7 +20790,7 @@
         <v>66</v>
       </c>
       <c r="BE97" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF97" s="6" t="s">
         <v>67</v>
@@ -20811,7 +20817,7 @@
         <v>66</v>
       </c>
       <c r="BN97" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO97" s="6" t="s">
         <v>67</v>
@@ -20819,10 +20825,10 @@
     </row>
     <row r="98" spans="1:67">
       <c r="A98" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>66</v>
@@ -20831,7 +20837,7 @@
         <v>66</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>32</v>
@@ -20879,7 +20885,7 @@
         <v>66</v>
       </c>
       <c r="U98" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V98" s="6" t="s">
         <v>67</v>
@@ -20906,7 +20912,7 @@
         <v>66</v>
       </c>
       <c r="AD98" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE98" s="6" t="s">
         <v>67</v>
@@ -20933,7 +20939,7 @@
         <v>66</v>
       </c>
       <c r="AM98" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN98" s="6" t="s">
         <v>67</v>
@@ -20960,7 +20966,7 @@
         <v>66</v>
       </c>
       <c r="AV98" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW98" s="6" t="s">
         <v>67</v>
@@ -20987,7 +20993,7 @@
         <v>66</v>
       </c>
       <c r="BE98" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF98" s="6" t="s">
         <v>67</v>
@@ -21014,7 +21020,7 @@
         <v>66</v>
       </c>
       <c r="BN98" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO98" s="6" t="s">
         <v>67</v>
@@ -21022,10 +21028,10 @@
     </row>
     <row r="99" spans="1:67">
       <c r="A99" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>66</v>
@@ -21034,7 +21040,7 @@
         <v>66</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>32</v>
@@ -21082,7 +21088,7 @@
         <v>66</v>
       </c>
       <c r="U99" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="V99" s="6" t="s">
         <v>67</v>
@@ -21109,7 +21115,7 @@
         <v>66</v>
       </c>
       <c r="AD99" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE99" s="6" t="s">
         <v>67</v>
@@ -21136,13 +21142,13 @@
         <v>66</v>
       </c>
       <c r="AM99" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN99" s="6" t="s">
         <v>67</v>
       </c>
       <c r="AO99" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP99" s="4" t="s">
         <v>32</v>
@@ -21169,7 +21175,7 @@
         <v>67</v>
       </c>
       <c r="AX99" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY99" s="4" t="s">
         <v>32</v>
@@ -21217,7 +21223,7 @@
         <v>66</v>
       </c>
       <c r="BN99" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO99" s="6" t="s">
         <v>67</v>
@@ -21225,10 +21231,10 @@
     </row>
     <row r="100" spans="1:67">
       <c r="A100" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>47</v>
@@ -21261,7 +21267,7 @@
         <v>33</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="N100" s="6" t="s">
         <v>31</v>
@@ -21288,7 +21294,7 @@
         <v>33</v>
       </c>
       <c r="V100" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="W100" s="6" t="s">
         <v>31</v>
@@ -21315,7 +21321,7 @@
         <v>33</v>
       </c>
       <c r="AE100" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AF100" s="6" t="s">
         <v>31</v>
@@ -21342,7 +21348,7 @@
         <v>33</v>
       </c>
       <c r="AN100" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AO100" s="6" t="s">
         <v>31</v>
@@ -21369,7 +21375,7 @@
         <v>33</v>
       </c>
       <c r="AW100" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AX100" s="6" t="s">
         <v>31</v>
@@ -21428,10 +21434,10 @@
     </row>
     <row r="101" spans="1:67">
       <c r="A101" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>58</v>
@@ -21440,7 +21446,7 @@
         <v>70</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>32</v>
@@ -21467,7 +21473,7 @@
         <v>77</v>
       </c>
       <c r="N101" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O101" s="4" t="s">
         <v>32</v>
@@ -21494,7 +21500,7 @@
         <v>77</v>
       </c>
       <c r="W101" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X101" s="4" t="s">
         <v>32</v>
@@ -21521,7 +21527,7 @@
         <v>77</v>
       </c>
       <c r="AF101" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG101" s="4" t="s">
         <v>32</v>
@@ -21602,7 +21608,7 @@
         <v>27</v>
       </c>
       <c r="BG101" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH101" s="4" t="s">
         <v>32</v>
@@ -21626,24 +21632,24 @@
         <v>33</v>
       </c>
       <c r="BO101" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="102" spans="1:67">
       <c r="A102" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>32</v>
@@ -21670,7 +21676,7 @@
         <v>77</v>
       </c>
       <c r="N102" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O102" s="4" t="s">
         <v>32</v>
@@ -21697,7 +21703,7 @@
         <v>77</v>
       </c>
       <c r="W102" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X102" s="4" t="s">
         <v>32</v>
@@ -21724,7 +21730,7 @@
         <v>77</v>
       </c>
       <c r="AF102" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG102" s="4" t="s">
         <v>32</v>
@@ -21805,7 +21811,7 @@
         <v>27</v>
       </c>
       <c r="BG102" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH102" s="4" t="s">
         <v>32</v>
@@ -21834,19 +21840,19 @@
     </row>
     <row r="103" spans="1:67">
       <c r="A103" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>32</v>
@@ -21873,7 +21879,7 @@
         <v>77</v>
       </c>
       <c r="N103" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O103" s="4" t="s">
         <v>32</v>
@@ -21900,7 +21906,7 @@
         <v>77</v>
       </c>
       <c r="W103" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X103" s="4" t="s">
         <v>32</v>
@@ -21927,7 +21933,7 @@
         <v>77</v>
       </c>
       <c r="AF103" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG103" s="4" t="s">
         <v>32</v>
@@ -22037,10 +22043,10 @@
     </row>
     <row r="104" spans="1:67">
       <c r="A104" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>58</v>
@@ -22240,10 +22246,10 @@
     </row>
     <row r="105" spans="1:67">
       <c r="A105" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>66</v>
@@ -22252,7 +22258,7 @@
         <v>66</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>32</v>
@@ -22279,7 +22285,7 @@
         <v>67</v>
       </c>
       <c r="N105" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O105" s="4" t="s">
         <v>32</v>
@@ -22327,7 +22333,7 @@
         <v>66</v>
       </c>
       <c r="AD105" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE105" s="6" t="s">
         <v>67</v>
@@ -22354,7 +22360,7 @@
         <v>66</v>
       </c>
       <c r="AM105" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN105" s="6" t="s">
         <v>67</v>
@@ -22381,7 +22387,7 @@
         <v>66</v>
       </c>
       <c r="AV105" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW105" s="6" t="s">
         <v>67</v>
@@ -22408,7 +22414,7 @@
         <v>66</v>
       </c>
       <c r="BE105" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF105" s="6" t="s">
         <v>67</v>
@@ -22435,7 +22441,7 @@
         <v>66</v>
       </c>
       <c r="BN105" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO105" s="6" t="s">
         <v>67</v>
@@ -22443,10 +22449,10 @@
     </row>
     <row r="106" spans="1:67">
       <c r="A106" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>66</v>
@@ -22455,7 +22461,7 @@
         <v>66</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>32</v>
@@ -22482,7 +22488,7 @@
         <v>67</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O106" s="4" t="s">
         <v>32</v>
@@ -22530,7 +22536,7 @@
         <v>66</v>
       </c>
       <c r="AD106" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE106" s="6" t="s">
         <v>67</v>
@@ -22557,7 +22563,7 @@
         <v>66</v>
       </c>
       <c r="AM106" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN106" s="6" t="s">
         <v>67</v>
@@ -22584,7 +22590,7 @@
         <v>66</v>
       </c>
       <c r="AV106" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW106" s="6" t="s">
         <v>67</v>
@@ -22611,7 +22617,7 @@
         <v>66</v>
       </c>
       <c r="BE106" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF106" s="6" t="s">
         <v>67</v>
@@ -22638,7 +22644,7 @@
         <v>66</v>
       </c>
       <c r="BN106" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO106" s="6" t="s">
         <v>67</v>
@@ -22646,10 +22652,10 @@
     </row>
     <row r="107" spans="1:67">
       <c r="A107" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>66</v>
@@ -22658,7 +22664,7 @@
         <v>66</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>32</v>
@@ -22685,7 +22691,7 @@
         <v>67</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O107" s="4" t="s">
         <v>32</v>
@@ -22733,7 +22739,7 @@
         <v>66</v>
       </c>
       <c r="AD107" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE107" s="6" t="s">
         <v>67</v>
@@ -22760,7 +22766,7 @@
         <v>66</v>
       </c>
       <c r="AM107" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN107" s="6" t="s">
         <v>67</v>
@@ -22787,7 +22793,7 @@
         <v>66</v>
       </c>
       <c r="AV107" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW107" s="6" t="s">
         <v>67</v>
@@ -22814,7 +22820,7 @@
         <v>66</v>
       </c>
       <c r="BE107" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF107" s="6" t="s">
         <v>67</v>
@@ -22841,7 +22847,7 @@
         <v>66</v>
       </c>
       <c r="BN107" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO107" s="6" t="s">
         <v>67</v>
@@ -22849,10 +22855,10 @@
     </row>
     <row r="108" spans="1:67">
       <c r="A108" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>66</v>
@@ -22861,7 +22867,7 @@
         <v>66</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>32</v>
@@ -22888,7 +22894,7 @@
         <v>67</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O108" s="4" t="s">
         <v>32</v>
@@ -22936,7 +22942,7 @@
         <v>66</v>
       </c>
       <c r="AD108" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE108" s="6" t="s">
         <v>67</v>
@@ -22963,7 +22969,7 @@
         <v>66</v>
       </c>
       <c r="AM108" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN108" s="6" t="s">
         <v>67</v>
@@ -22990,7 +22996,7 @@
         <v>66</v>
       </c>
       <c r="AV108" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW108" s="6" t="s">
         <v>67</v>
@@ -23017,7 +23023,7 @@
         <v>66</v>
       </c>
       <c r="BE108" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF108" s="6" t="s">
         <v>67</v>
@@ -23044,7 +23050,7 @@
         <v>66</v>
       </c>
       <c r="BN108" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO108" s="6" t="s">
         <v>67</v>
@@ -23052,10 +23058,10 @@
     </row>
     <row r="109" spans="1:67">
       <c r="A109" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>66</v>
@@ -23064,7 +23070,7 @@
         <v>66</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>32</v>
@@ -23091,7 +23097,7 @@
         <v>67</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O109" s="4" t="s">
         <v>32</v>
@@ -23139,7 +23145,7 @@
         <v>66</v>
       </c>
       <c r="AD109" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AE109" s="6" t="s">
         <v>67</v>
@@ -23166,7 +23172,7 @@
         <v>66</v>
       </c>
       <c r="AM109" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AN109" s="6" t="s">
         <v>67</v>
@@ -23193,7 +23199,7 @@
         <v>66</v>
       </c>
       <c r="AV109" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AW109" s="6" t="s">
         <v>67</v>
@@ -23220,7 +23226,7 @@
         <v>66</v>
       </c>
       <c r="BE109" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BF109" s="6" t="s">
         <v>67</v>
@@ -23247,7 +23253,7 @@
         <v>66</v>
       </c>
       <c r="BN109" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO109" s="6" t="s">
         <v>67</v>
@@ -23255,10 +23261,10 @@
     </row>
     <row r="110" spans="1:67">
       <c r="A110" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>47</v>
@@ -23294,7 +23300,7 @@
         <v>27</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O110" s="4" t="s">
         <v>32</v>
@@ -23458,10 +23464,10 @@
     </row>
     <row r="111" spans="1:67">
       <c r="A111" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>47</v>
@@ -23661,10 +23667,10 @@
     </row>
     <row r="112" spans="1:67">
       <c r="A112" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>47</v>
@@ -23864,10 +23870,10 @@
     </row>
     <row r="113" spans="1:67">
       <c r="A113" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>47</v>
@@ -24067,10 +24073,10 @@
     </row>
     <row r="114" spans="1:67">
       <c r="A114" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>47</v>
@@ -24270,10 +24276,10 @@
     </row>
     <row r="115" spans="1:67">
       <c r="A115" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>47</v>
@@ -24473,10 +24479,10 @@
     </row>
     <row r="116" spans="1:67">
       <c r="A116" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>58</v>
@@ -24676,10 +24682,10 @@
     </row>
     <row r="117" spans="1:67">
       <c r="A117" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>58</v>
@@ -24879,10 +24885,10 @@
     </row>
     <row r="118" spans="1:67">
       <c r="A118" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>47</v>
@@ -24969,7 +24975,7 @@
         <v>33</v>
       </c>
       <c r="AE118" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="AF118" s="5" t="s">
         <v>25</v>
@@ -25082,10 +25088,10 @@
     </row>
     <row r="119" spans="1:67">
       <c r="A119" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>58</v>
@@ -25094,7 +25100,7 @@
         <v>73</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>32</v>
@@ -25121,7 +25127,7 @@
         <v>77</v>
       </c>
       <c r="N119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O119" s="4" t="s">
         <v>32</v>
@@ -25148,7 +25154,7 @@
         <v>77</v>
       </c>
       <c r="W119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X119" s="4" t="s">
         <v>32</v>
@@ -25175,7 +25181,7 @@
         <v>77</v>
       </c>
       <c r="AF119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG119" s="4" t="s">
         <v>32</v>
@@ -25202,7 +25208,7 @@
         <v>77</v>
       </c>
       <c r="AO119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP119" s="4" t="s">
         <v>32</v>
@@ -25229,7 +25235,7 @@
         <v>77</v>
       </c>
       <c r="AX119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY119" s="4" t="s">
         <v>32</v>
@@ -25256,7 +25262,7 @@
         <v>77</v>
       </c>
       <c r="BG119" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH119" s="4" t="s">
         <v>32</v>
@@ -25285,10 +25291,10 @@
     </row>
     <row r="120" spans="1:67">
       <c r="A120" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>47</v>
@@ -25488,10 +25494,10 @@
     </row>
     <row r="121" spans="1:67">
       <c r="A121" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>66</v>
@@ -25500,7 +25506,7 @@
         <v>66</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>32</v>
@@ -25527,7 +25533,7 @@
         <v>67</v>
       </c>
       <c r="N121" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O121" s="4" t="s">
         <v>32</v>
@@ -25554,7 +25560,7 @@
         <v>67</v>
       </c>
       <c r="W121" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X121" s="4" t="s">
         <v>32</v>
@@ -25581,7 +25587,7 @@
         <v>67</v>
       </c>
       <c r="AF121" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG121" s="4" t="s">
         <v>32</v>
@@ -25608,7 +25614,7 @@
         <v>67</v>
       </c>
       <c r="AO121" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP121" s="4" t="s">
         <v>32</v>
@@ -25635,7 +25641,7 @@
         <v>67</v>
       </c>
       <c r="AX121" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY121" s="4" t="s">
         <v>32</v>
@@ -25683,7 +25689,7 @@
         <v>66</v>
       </c>
       <c r="BN121" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BO121" s="6" t="s">
         <v>67</v>
@@ -25691,19 +25697,19 @@
     </row>
     <row r="122" spans="1:67">
       <c r="A122" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>32</v>
@@ -25730,7 +25736,7 @@
         <v>77</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O122" s="4" t="s">
         <v>32</v>
@@ -25757,7 +25763,7 @@
         <v>77</v>
       </c>
       <c r="W122" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X122" s="4" t="s">
         <v>32</v>
@@ -25784,7 +25790,7 @@
         <v>77</v>
       </c>
       <c r="AF122" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG122" s="4" t="s">
         <v>32</v>
@@ -25865,7 +25871,7 @@
         <v>27</v>
       </c>
       <c r="BG122" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH122" s="4" t="s">
         <v>32</v>
@@ -25894,19 +25900,19 @@
     </row>
     <row r="123" spans="1:67">
       <c r="A123" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>32</v>
@@ -25933,7 +25939,7 @@
         <v>77</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O123" s="4" t="s">
         <v>32</v>
@@ -25960,7 +25966,7 @@
         <v>77</v>
       </c>
       <c r="W123" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X123" s="4" t="s">
         <v>32</v>
@@ -25987,7 +25993,7 @@
         <v>77</v>
       </c>
       <c r="AF123" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG123" s="4" t="s">
         <v>32</v>
@@ -26097,10 +26103,10 @@
     </row>
     <row r="124" spans="1:67">
       <c r="A124" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>47</v>
@@ -26109,7 +26115,7 @@
         <v>61</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>32</v>
@@ -26300,10 +26306,10 @@
     </row>
     <row r="125" spans="1:67">
       <c r="A125" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>47</v>
@@ -26312,7 +26318,7 @@
         <v>61</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>32</v>
@@ -26503,10 +26509,10 @@
     </row>
     <row r="126" spans="1:67">
       <c r="A126" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>29</v>
@@ -26515,7 +26521,7 @@
         <v>63</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>32</v>
@@ -26544,8 +26550,8 @@
       <c r="N126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O126" s="5" t="s">
-        <v>26</v>
+      <c r="O126" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P126" s="4" t="s">
         <v>32</v>
@@ -26566,13 +26572,13 @@
         <v>33</v>
       </c>
       <c r="V126" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X126" s="5" t="s">
-        <v>26</v>
+      <c r="X126" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y126" s="4" t="s">
         <v>32</v>
@@ -26593,13 +26599,13 @@
         <v>33</v>
       </c>
       <c r="AE126" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG126" s="5" t="s">
-        <v>26</v>
+      <c r="AG126" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH126" s="4" t="s">
         <v>32</v>
@@ -26620,13 +26626,13 @@
         <v>33</v>
       </c>
       <c r="AN126" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP126" s="5" t="s">
-        <v>26</v>
+      <c r="AP126" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ126" s="4" t="s">
         <v>32</v>
@@ -26647,13 +26653,13 @@
         <v>33</v>
       </c>
       <c r="AW126" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY126" s="5" t="s">
-        <v>26</v>
+      <c r="AY126" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ126" s="4" t="s">
         <v>32</v>
@@ -26674,13 +26680,13 @@
         <v>33</v>
       </c>
       <c r="BF126" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH126" s="5" t="s">
-        <v>26</v>
+      <c r="BH126" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI126" s="4" t="s">
         <v>32</v>
@@ -26701,15 +26707,15 @@
         <v>33</v>
       </c>
       <c r="BO126" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:67">
       <c r="A127" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>29</v>
@@ -26718,7 +26724,7 @@
         <v>63</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>32</v>
@@ -26747,8 +26753,8 @@
       <c r="N127" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O127" s="5" t="s">
-        <v>26</v>
+      <c r="O127" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P127" s="4" t="s">
         <v>32</v>
@@ -26769,13 +26775,13 @@
         <v>33</v>
       </c>
       <c r="V127" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W127" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X127" s="5" t="s">
-        <v>26</v>
+      <c r="X127" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y127" s="4" t="s">
         <v>32</v>
@@ -26796,13 +26802,13 @@
         <v>33</v>
       </c>
       <c r="AE127" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF127" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG127" s="5" t="s">
-        <v>26</v>
+      <c r="AG127" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH127" s="4" t="s">
         <v>32</v>
@@ -26823,13 +26829,13 @@
         <v>33</v>
       </c>
       <c r="AN127" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO127" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP127" s="5" t="s">
-        <v>26</v>
+      <c r="AP127" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ127" s="4" t="s">
         <v>32</v>
@@ -26850,13 +26856,13 @@
         <v>33</v>
       </c>
       <c r="AW127" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX127" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY127" s="5" t="s">
-        <v>26</v>
+      <c r="AY127" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ127" s="4" t="s">
         <v>32</v>
@@ -26877,13 +26883,13 @@
         <v>33</v>
       </c>
       <c r="BF127" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG127" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH127" s="5" t="s">
-        <v>26</v>
+      <c r="BH127" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI127" s="4" t="s">
         <v>32</v>
@@ -26904,21 +26910,21 @@
         <v>33</v>
       </c>
       <c r="BO127" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="128" spans="1:67">
       <c r="A128" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>31</v>
@@ -26945,7 +26951,7 @@
         <v>33</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="N128" s="6" t="s">
         <v>31</v>
@@ -26972,7 +26978,7 @@
         <v>33</v>
       </c>
       <c r="V128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="W128" s="6" t="s">
         <v>31</v>
@@ -26999,7 +27005,7 @@
         <v>33</v>
       </c>
       <c r="AE128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="AF128" s="6" t="s">
         <v>31</v>
@@ -27026,7 +27032,7 @@
         <v>33</v>
       </c>
       <c r="AN128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="AO128" s="6" t="s">
         <v>31</v>
@@ -27053,7 +27059,7 @@
         <v>33</v>
       </c>
       <c r="AW128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="AX128" s="6" t="s">
         <v>31</v>
@@ -27080,7 +27086,7 @@
         <v>33</v>
       </c>
       <c r="BF128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="BG128" s="6" t="s">
         <v>31</v>
@@ -27107,15 +27113,15 @@
         <v>33</v>
       </c>
       <c r="BO128" s="7" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:67">
       <c r="A129" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>29</v>
@@ -27124,7 +27130,7 @@
         <v>63</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>32</v>
@@ -27153,8 +27159,8 @@
       <c r="N129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O129" s="5" t="s">
-        <v>26</v>
+      <c r="O129" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P129" s="4" t="s">
         <v>32</v>
@@ -27175,13 +27181,13 @@
         <v>33</v>
       </c>
       <c r="V129" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X129" s="5" t="s">
-        <v>26</v>
+      <c r="X129" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y129" s="4" t="s">
         <v>32</v>
@@ -27202,13 +27208,13 @@
         <v>33</v>
       </c>
       <c r="AE129" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG129" s="5" t="s">
-        <v>26</v>
+      <c r="AG129" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH129" s="4" t="s">
         <v>32</v>
@@ -27229,13 +27235,13 @@
         <v>33</v>
       </c>
       <c r="AN129" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP129" s="5" t="s">
-        <v>26</v>
+      <c r="AP129" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ129" s="4" t="s">
         <v>32</v>
@@ -27256,13 +27262,13 @@
         <v>33</v>
       </c>
       <c r="AW129" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY129" s="5" t="s">
-        <v>26</v>
+      <c r="AY129" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ129" s="4" t="s">
         <v>32</v>
@@ -27283,13 +27289,13 @@
         <v>33</v>
       </c>
       <c r="BF129" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH129" s="5" t="s">
-        <v>26</v>
+      <c r="BH129" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI129" s="4" t="s">
         <v>32</v>
@@ -27310,15 +27316,15 @@
         <v>33</v>
       </c>
       <c r="BO129" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:67">
       <c r="A130" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>29</v>
@@ -27327,7 +27333,7 @@
         <v>63</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>32</v>
@@ -27356,8 +27362,8 @@
       <c r="N130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O130" s="5" t="s">
-        <v>26</v>
+      <c r="O130" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P130" s="4" t="s">
         <v>32</v>
@@ -27378,13 +27384,13 @@
         <v>33</v>
       </c>
       <c r="V130" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="W130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X130" s="5" t="s">
-        <v>26</v>
+      <c r="X130" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="Y130" s="4" t="s">
         <v>32</v>
@@ -27405,13 +27411,13 @@
         <v>33</v>
       </c>
       <c r="AE130" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG130" s="5" t="s">
-        <v>26</v>
+      <c r="AG130" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AH130" s="4" t="s">
         <v>32</v>
@@ -27432,13 +27438,13 @@
         <v>33</v>
       </c>
       <c r="AN130" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AO130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP130" s="5" t="s">
-        <v>26</v>
+      <c r="AP130" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AQ130" s="4" t="s">
         <v>32</v>
@@ -27459,13 +27465,13 @@
         <v>33</v>
       </c>
       <c r="AW130" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AX130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AY130" s="5" t="s">
-        <v>26</v>
+      <c r="AY130" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="AZ130" s="4" t="s">
         <v>32</v>
@@ -27486,13 +27492,13 @@
         <v>33</v>
       </c>
       <c r="BF130" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="BG130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH130" s="5" t="s">
-        <v>26</v>
+      <c r="BH130" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="BI130" s="4" t="s">
         <v>32</v>
@@ -27513,15 +27519,15 @@
         <v>33</v>
       </c>
       <c r="BO130" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:67">
       <c r="A131" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>23</v>
@@ -27721,19 +27727,19 @@
     </row>
     <row r="132" spans="1:67">
       <c r="A132" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>32</v>
@@ -27760,7 +27766,7 @@
         <v>77</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O132" s="4" t="s">
         <v>32</v>
@@ -27787,7 +27793,7 @@
         <v>77</v>
       </c>
       <c r="W132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X132" s="4" t="s">
         <v>32</v>
@@ -27814,7 +27820,7 @@
         <v>77</v>
       </c>
       <c r="AF132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG132" s="4" t="s">
         <v>32</v>
@@ -27841,7 +27847,7 @@
         <v>77</v>
       </c>
       <c r="AO132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP132" s="4" t="s">
         <v>32</v>
@@ -27868,7 +27874,7 @@
         <v>77</v>
       </c>
       <c r="AX132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY132" s="4" t="s">
         <v>32</v>
@@ -27895,7 +27901,7 @@
         <v>77</v>
       </c>
       <c r="BG132" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH132" s="4" t="s">
         <v>32</v>
@@ -27924,10 +27930,10 @@
     </row>
     <row r="133" spans="1:67">
       <c r="A133" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>66</v>
@@ -27936,7 +27942,7 @@
         <v>66</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>32</v>
@@ -27963,7 +27969,7 @@
         <v>67</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O133" s="4" t="s">
         <v>32</v>
@@ -27990,7 +27996,7 @@
         <v>67</v>
       </c>
       <c r="W133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X133" s="4" t="s">
         <v>32</v>
@@ -28017,7 +28023,7 @@
         <v>67</v>
       </c>
       <c r="AF133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG133" s="4" t="s">
         <v>32</v>
@@ -28044,7 +28050,7 @@
         <v>67</v>
       </c>
       <c r="AO133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP133" s="4" t="s">
         <v>32</v>
@@ -28071,7 +28077,7 @@
         <v>67</v>
       </c>
       <c r="AX133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY133" s="4" t="s">
         <v>32</v>
@@ -28098,7 +28104,7 @@
         <v>67</v>
       </c>
       <c r="BG133" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH133" s="4" t="s">
         <v>32</v>
@@ -28127,10 +28133,10 @@
     </row>
     <row r="134" spans="1:67">
       <c r="A134" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>66</v>
@@ -28139,7 +28145,7 @@
         <v>66</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>32</v>
@@ -28166,7 +28172,7 @@
         <v>67</v>
       </c>
       <c r="N134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O134" s="4" t="s">
         <v>32</v>
@@ -28193,7 +28199,7 @@
         <v>67</v>
       </c>
       <c r="W134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X134" s="4" t="s">
         <v>32</v>
@@ -28220,7 +28226,7 @@
         <v>67</v>
       </c>
       <c r="AF134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG134" s="4" t="s">
         <v>32</v>
@@ -28247,7 +28253,7 @@
         <v>67</v>
       </c>
       <c r="AO134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP134" s="4" t="s">
         <v>32</v>
@@ -28274,7 +28280,7 @@
         <v>67</v>
       </c>
       <c r="AX134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY134" s="4" t="s">
         <v>32</v>
@@ -28301,7 +28307,7 @@
         <v>67</v>
       </c>
       <c r="BG134" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH134" s="4" t="s">
         <v>32</v>
@@ -28330,10 +28336,10 @@
     </row>
     <row r="135" spans="1:67">
       <c r="A135" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>66</v>
@@ -28342,7 +28348,7 @@
         <v>66</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>32</v>
@@ -28369,7 +28375,7 @@
         <v>67</v>
       </c>
       <c r="N135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O135" s="4" t="s">
         <v>32</v>
@@ -28396,7 +28402,7 @@
         <v>67</v>
       </c>
       <c r="W135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X135" s="4" t="s">
         <v>32</v>
@@ -28423,7 +28429,7 @@
         <v>67</v>
       </c>
       <c r="AF135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG135" s="4" t="s">
         <v>32</v>
@@ -28450,7 +28456,7 @@
         <v>67</v>
       </c>
       <c r="AO135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP135" s="4" t="s">
         <v>32</v>
@@ -28477,7 +28483,7 @@
         <v>67</v>
       </c>
       <c r="AX135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY135" s="4" t="s">
         <v>32</v>
@@ -28504,7 +28510,7 @@
         <v>67</v>
       </c>
       <c r="BG135" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH135" s="4" t="s">
         <v>32</v>
@@ -28533,10 +28539,10 @@
     </row>
     <row r="136" spans="1:67">
       <c r="A136" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>66</v>
@@ -28545,7 +28551,7 @@
         <v>66</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>32</v>
@@ -28572,7 +28578,7 @@
         <v>67</v>
       </c>
       <c r="N136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O136" s="4" t="s">
         <v>32</v>
@@ -28599,7 +28605,7 @@
         <v>67</v>
       </c>
       <c r="W136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X136" s="4" t="s">
         <v>32</v>
@@ -28626,7 +28632,7 @@
         <v>67</v>
       </c>
       <c r="AF136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG136" s="4" t="s">
         <v>32</v>
@@ -28653,7 +28659,7 @@
         <v>67</v>
       </c>
       <c r="AO136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP136" s="4" t="s">
         <v>32</v>
@@ -28680,7 +28686,7 @@
         <v>67</v>
       </c>
       <c r="AX136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY136" s="4" t="s">
         <v>32</v>
@@ -28707,7 +28713,7 @@
         <v>67</v>
       </c>
       <c r="BG136" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH136" s="4" t="s">
         <v>32</v>
@@ -28736,10 +28742,10 @@
     </row>
     <row r="137" spans="1:67">
       <c r="A137" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>66</v>
@@ -28748,7 +28754,7 @@
         <v>66</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>32</v>
@@ -28775,7 +28781,7 @@
         <v>67</v>
       </c>
       <c r="N137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O137" s="4" t="s">
         <v>32</v>
@@ -28802,7 +28808,7 @@
         <v>67</v>
       </c>
       <c r="W137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X137" s="4" t="s">
         <v>32</v>
@@ -28829,7 +28835,7 @@
         <v>67</v>
       </c>
       <c r="AF137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG137" s="4" t="s">
         <v>32</v>
@@ -28856,7 +28862,7 @@
         <v>67</v>
       </c>
       <c r="AO137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP137" s="4" t="s">
         <v>32</v>
@@ -28883,7 +28889,7 @@
         <v>67</v>
       </c>
       <c r="AX137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY137" s="4" t="s">
         <v>32</v>
@@ -28910,7 +28916,7 @@
         <v>67</v>
       </c>
       <c r="BG137" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH137" s="4" t="s">
         <v>32</v>
@@ -28939,10 +28945,10 @@
     </row>
     <row r="138" spans="1:67">
       <c r="A138" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>66</v>
@@ -28951,7 +28957,7 @@
         <v>66</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>32</v>
@@ -28978,7 +28984,7 @@
         <v>67</v>
       </c>
       <c r="N138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O138" s="4" t="s">
         <v>32</v>
@@ -29005,7 +29011,7 @@
         <v>67</v>
       </c>
       <c r="W138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X138" s="4" t="s">
         <v>32</v>
@@ -29032,7 +29038,7 @@
         <v>67</v>
       </c>
       <c r="AF138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG138" s="4" t="s">
         <v>32</v>
@@ -29059,7 +29065,7 @@
         <v>67</v>
       </c>
       <c r="AO138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP138" s="4" t="s">
         <v>32</v>
@@ -29086,7 +29092,7 @@
         <v>67</v>
       </c>
       <c r="AX138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY138" s="4" t="s">
         <v>32</v>
@@ -29113,7 +29119,7 @@
         <v>67</v>
       </c>
       <c r="BG138" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH138" s="4" t="s">
         <v>32</v>
@@ -29142,10 +29148,10 @@
     </row>
     <row r="139" spans="1:67">
       <c r="A139" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>66</v>
@@ -29154,7 +29160,7 @@
         <v>66</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>32</v>
@@ -29181,7 +29187,7 @@
         <v>67</v>
       </c>
       <c r="N139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O139" s="4" t="s">
         <v>32</v>
@@ -29208,7 +29214,7 @@
         <v>67</v>
       </c>
       <c r="W139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X139" s="4" t="s">
         <v>32</v>
@@ -29235,7 +29241,7 @@
         <v>67</v>
       </c>
       <c r="AF139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG139" s="4" t="s">
         <v>32</v>
@@ -29262,7 +29268,7 @@
         <v>67</v>
       </c>
       <c r="AO139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP139" s="4" t="s">
         <v>32</v>
@@ -29289,7 +29295,7 @@
         <v>67</v>
       </c>
       <c r="AX139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY139" s="4" t="s">
         <v>32</v>
@@ -29316,7 +29322,7 @@
         <v>67</v>
       </c>
       <c r="BG139" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH139" s="4" t="s">
         <v>32</v>
@@ -29345,10 +29351,10 @@
     </row>
     <row r="140" spans="1:67">
       <c r="A140" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>66</v>
@@ -29357,7 +29363,7 @@
         <v>66</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>32</v>
@@ -29384,7 +29390,7 @@
         <v>67</v>
       </c>
       <c r="N140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O140" s="4" t="s">
         <v>32</v>
@@ -29411,7 +29417,7 @@
         <v>67</v>
       </c>
       <c r="W140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X140" s="4" t="s">
         <v>32</v>
@@ -29438,7 +29444,7 @@
         <v>67</v>
       </c>
       <c r="AF140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG140" s="4" t="s">
         <v>32</v>
@@ -29465,7 +29471,7 @@
         <v>67</v>
       </c>
       <c r="AO140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AP140" s="4" t="s">
         <v>32</v>
@@ -29492,7 +29498,7 @@
         <v>67</v>
       </c>
       <c r="AX140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY140" s="4" t="s">
         <v>32</v>
@@ -29519,7 +29525,7 @@
         <v>67</v>
       </c>
       <c r="BG140" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH140" s="4" t="s">
         <v>32</v>
@@ -29575,19 +29581,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -29595,10 +29601,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" s="7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D2" s="6">
         <v>31</v>
@@ -29612,10 +29618,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C3" s="7">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D3" s="6">
         <v>31</v>
@@ -29629,10 +29635,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C4" s="7">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D4" s="6">
         <v>31</v>
@@ -29646,10 +29652,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C5" s="7">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D5" s="6">
         <v>31</v>
@@ -29663,10 +29669,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C6" s="7">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D6" s="6">
         <v>31</v>
@@ -29680,10 +29686,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C7" s="7">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6">
         <v>31</v>
@@ -29697,10 +29703,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C8" s="7">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D8" s="6">
         <v>31</v>

--- a/Brew_Comparison.xlsx
+++ b/Brew_Comparison.xlsx
@@ -78,11 +78,11 @@
   </si>
   <si>
     <t>Exp
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>Exp
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>DB
@@ -102,11 +102,11 @@
   </si>
   <si>
     <t>DB
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>DB
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>Match</t>
@@ -130,7 +130,7 @@
     <t>X</t>
   </si>
   <si>
-    <t>NO</t>
+    <t>NC</t>
   </si>
   <si>
     <t>T</t>
@@ -172,7 +172,7 @@
     <t>EM - 212</t>
   </si>
   <si>
-    <t>NC</t>
+    <t>NO</t>
   </si>
   <si>
     <t>AV220-1</t>
